--- a/research/traditional_assets/database/data/germany/germany_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_oil_gas_distribution.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07031265058164095</v>
+        <v>0.07013321262989602</v>
       </c>
       <c r="C2">
-        <v>573.609412046684</v>
+        <v>571.4756184468529</v>
       </c>
       <c r="D2">
-        <v>515.609412046684</v>
+        <v>519.4116184468529</v>
       </c>
       <c r="E2">
-        <v>-37.59999999999999</v>
+        <v>-31.66399999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.936</v>
       </c>
       <c r="G2">
         <v>58</v>
@@ -1439,28 +1439,28 @@
         <v>29.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2985808</v>
       </c>
       <c r="N2">
-        <v>29.4</v>
+        <v>29.1014192</v>
       </c>
       <c r="O2">
-        <v>8.819999999999999</v>
+        <v>8.730425759999999</v>
       </c>
       <c r="P2">
-        <v>20.58</v>
+        <v>20.37099344</v>
       </c>
       <c r="Q2">
-        <v>43.08</v>
+        <v>42.87099344</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07031265058164095</v>
+        <v>0.07048597235343033</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5701148349522017</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>98.46580892006452</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07013321262989602</v>
+        <v>0.0699537746781511</v>
       </c>
       <c r="C3">
-        <v>571.4756184468529</v>
+        <v>569.3983178910822</v>
       </c>
       <c r="D3">
-        <v>519.4116184468529</v>
+        <v>523.2703178910822</v>
       </c>
       <c r="E3">
-        <v>-31.66399999999999</v>
+        <v>-25.72799999999999</v>
       </c>
       <c r="F3">
-        <v>5.936</v>
+        <v>11.872</v>
       </c>
       <c r="G3">
         <v>58</v>
@@ -1521,28 +1521,28 @@
         <v>29.4</v>
       </c>
       <c r="M3">
-        <v>0.2985808</v>
+        <v>0.5971616</v>
       </c>
       <c r="N3">
-        <v>29.1014192</v>
+        <v>28.8028384</v>
       </c>
       <c r="O3">
-        <v>8.730425759999999</v>
+        <v>8.64085152</v>
       </c>
       <c r="P3">
-        <v>20.37099344</v>
+        <v>20.16198688</v>
       </c>
       <c r="Q3">
-        <v>42.87099344</v>
+        <v>42.66198688</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07048597235343033</v>
+        <v>0.07066283130423581</v>
       </c>
       <c r="T3">
-        <v>0.5701148349522017</v>
+        <v>0.5741993372802731</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>98.46580892006452</v>
+        <v>49.23290446003226</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0699537746781511</v>
+        <v>0.06977433672640618</v>
       </c>
       <c r="C4">
-        <v>569.3983178910822</v>
+        <v>567.3787788602765</v>
       </c>
       <c r="D4">
-        <v>523.2703178910822</v>
+        <v>527.1867788602765</v>
       </c>
       <c r="E4">
-        <v>-25.72799999999999</v>
+        <v>-19.79199999999999</v>
       </c>
       <c r="F4">
-        <v>11.872</v>
+        <v>17.808</v>
       </c>
       <c r="G4">
         <v>58</v>
@@ -1603,28 +1603,28 @@
         <v>29.4</v>
       </c>
       <c r="M4">
-        <v>0.5971616</v>
+        <v>0.8957423999999999</v>
       </c>
       <c r="N4">
-        <v>28.8028384</v>
+        <v>28.5042576</v>
       </c>
       <c r="O4">
-        <v>8.64085152</v>
+        <v>8.551277279999999</v>
       </c>
       <c r="P4">
-        <v>20.16198688</v>
+        <v>19.95298032</v>
       </c>
       <c r="Q4">
-        <v>42.66198688</v>
+        <v>42.45298032</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07066283130423581</v>
+        <v>0.07084333683134658</v>
       </c>
       <c r="T4">
-        <v>0.5741993372802731</v>
+        <v>0.5783680561511912</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>49.23290446003226</v>
+        <v>32.82193630668817</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06977433672640618</v>
+        <v>0.06959489877466125</v>
       </c>
       <c r="C5">
-        <v>567.3787788602765</v>
+        <v>565.4183080979308</v>
       </c>
       <c r="D5">
-        <v>527.1867788602765</v>
+        <v>531.1623080979308</v>
       </c>
       <c r="E5">
-        <v>-19.79199999999999</v>
+        <v>-13.85599999999999</v>
       </c>
       <c r="F5">
-        <v>17.808</v>
+        <v>23.744</v>
       </c>
       <c r="G5">
         <v>58</v>
@@ -1685,28 +1685,28 @@
         <v>29.4</v>
       </c>
       <c r="M5">
-        <v>0.8957423999999999</v>
+        <v>1.1943232</v>
       </c>
       <c r="N5">
-        <v>28.5042576</v>
+        <v>28.2056768</v>
       </c>
       <c r="O5">
-        <v>8.551277279999999</v>
+        <v>8.46170304</v>
       </c>
       <c r="P5">
-        <v>19.95298032</v>
+        <v>19.74397376</v>
       </c>
       <c r="Q5">
-        <v>42.45298032</v>
+        <v>42.24397376</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07084333683134658</v>
+        <v>0.07102760289027214</v>
       </c>
       <c r="T5">
-        <v>0.5783680561511912</v>
+        <v>0.5826236233319203</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>32.82193630668817</v>
+        <v>24.61645223001613</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06959489877466125</v>
+        <v>0.06941546082291633</v>
       </c>
       <c r="C6">
-        <v>565.4183080979308</v>
+        <v>563.5182520637886</v>
       </c>
       <c r="D6">
-        <v>531.1623080979308</v>
+        <v>535.1982520637886</v>
       </c>
       <c r="E6">
-        <v>-13.85599999999999</v>
+        <v>-7.919999999999991</v>
       </c>
       <c r="F6">
-        <v>23.744</v>
+        <v>29.68</v>
       </c>
       <c r="G6">
         <v>58</v>
@@ -1767,28 +1767,28 @@
         <v>29.4</v>
       </c>
       <c r="M6">
-        <v>1.1943232</v>
+        <v>1.492904</v>
       </c>
       <c r="N6">
-        <v>28.2056768</v>
+        <v>27.907096</v>
       </c>
       <c r="O6">
-        <v>8.46170304</v>
+        <v>8.372128799999999</v>
       </c>
       <c r="P6">
-        <v>19.74397376</v>
+        <v>19.5349672</v>
       </c>
       <c r="Q6">
-        <v>42.24397376</v>
+        <v>42.0349672</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07102760289027214</v>
+        <v>0.07121574823464877</v>
       </c>
       <c r="T6">
-        <v>0.5826236233319203</v>
+        <v>0.5869687814006647</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.61645223001613</v>
+        <v>19.6931617840129</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06941546082291633</v>
+        <v>0.06923602287117141</v>
       </c>
       <c r="C7">
-        <v>563.5182520637886</v>
+        <v>561.6799984542788</v>
       </c>
       <c r="D7">
-        <v>535.1982520637886</v>
+        <v>539.2959984542788</v>
       </c>
       <c r="E7">
-        <v>-7.919999999999991</v>
+        <v>-1.983999999999988</v>
       </c>
       <c r="F7">
-        <v>29.68</v>
+        <v>35.61600000000001</v>
       </c>
       <c r="G7">
         <v>58</v>
@@ -1849,28 +1849,28 @@
         <v>29.4</v>
       </c>
       <c r="M7">
-        <v>1.492904</v>
+        <v>1.7914848</v>
       </c>
       <c r="N7">
-        <v>27.907096</v>
+        <v>27.6085152</v>
       </c>
       <c r="O7">
-        <v>8.372128799999999</v>
+        <v>8.282554559999999</v>
       </c>
       <c r="P7">
-        <v>19.5349672</v>
+        <v>19.32596064</v>
       </c>
       <c r="Q7">
-        <v>42.0349672</v>
+        <v>41.82596064</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07121574823464877</v>
+        <v>0.07140789667145894</v>
       </c>
       <c r="T7">
-        <v>0.5869687814006647</v>
+        <v>0.5914063896410844</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.6931617840129</v>
+        <v>16.41096815334408</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06923602287117141</v>
+        <v>0.0690565849194265</v>
       </c>
       <c r="C8">
-        <v>561.6799984542788</v>
+        <v>559.9049777933402</v>
       </c>
       <c r="D8">
-        <v>539.2959984542788</v>
+        <v>543.4569777933402</v>
       </c>
       <c r="E8">
-        <v>-1.983999999999995</v>
+        <v>3.952000000000005</v>
       </c>
       <c r="F8">
-        <v>35.616</v>
+        <v>41.552</v>
       </c>
       <c r="G8">
         <v>58</v>
@@ -1931,28 +1931,28 @@
         <v>29.4</v>
       </c>
       <c r="M8">
-        <v>1.7914848</v>
+        <v>2.0900656</v>
       </c>
       <c r="N8">
-        <v>27.6085152</v>
+        <v>27.3099344</v>
       </c>
       <c r="O8">
-        <v>8.282554559999999</v>
+        <v>8.19298032</v>
       </c>
       <c r="P8">
-        <v>19.32596064</v>
+        <v>19.11695408</v>
       </c>
       <c r="Q8">
-        <v>41.82596064</v>
+        <v>41.61695408</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07140789667145894</v>
+        <v>0.07160417733271666</v>
       </c>
       <c r="T8">
-        <v>0.5914063896410844</v>
+        <v>0.5959394303167821</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.41096815334409</v>
+        <v>14.06654413143779</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0690565849194265</v>
+        <v>0.06896114696768157</v>
       </c>
       <c r="C9">
-        <v>559.9049777933402</v>
+        <v>556.2083496558157</v>
       </c>
       <c r="D9">
-        <v>543.4569777933402</v>
+        <v>545.6963496558157</v>
       </c>
       <c r="E9">
-        <v>3.952000000000012</v>
+        <v>9.888000000000005</v>
       </c>
       <c r="F9">
-        <v>41.55200000000001</v>
+        <v>47.488</v>
       </c>
       <c r="G9">
         <v>58</v>
@@ -2013,45 +2013,45 @@
         <v>29.4</v>
       </c>
       <c r="M9">
-        <v>2.0900656</v>
+        <v>2.4598784</v>
       </c>
       <c r="N9">
-        <v>27.3099344</v>
+        <v>26.9401216</v>
       </c>
       <c r="O9">
-        <v>8.19298032</v>
+        <v>8.082036479999999</v>
       </c>
       <c r="P9">
-        <v>19.11695408</v>
+        <v>18.85808512</v>
       </c>
       <c r="Q9">
-        <v>41.61695408</v>
+        <v>41.35808512</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07160417733271666</v>
+        <v>0.07180472496487128</v>
       </c>
       <c r="T9">
-        <v>0.5959394303167821</v>
+        <v>0.6005710153549949</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>14.06654413143779</v>
+        <v>11.9518103008669</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06896114696768157</v>
+        <v>0.06879220901593665</v>
       </c>
       <c r="C10">
-        <v>556.2083496558157</v>
+        <v>554.2819175716969</v>
       </c>
       <c r="D10">
-        <v>545.6963496558157</v>
+        <v>549.7059175716969</v>
       </c>
       <c r="E10">
-        <v>9.888000000000005</v>
+        <v>15.82400000000001</v>
       </c>
       <c r="F10">
-        <v>47.488</v>
+        <v>53.424</v>
       </c>
       <c r="G10">
         <v>58</v>
@@ -2095,28 +2095,28 @@
         <v>29.4</v>
       </c>
       <c r="M10">
-        <v>2.4598784</v>
+        <v>2.7673632</v>
       </c>
       <c r="N10">
-        <v>26.9401216</v>
+        <v>26.6326368</v>
       </c>
       <c r="O10">
-        <v>8.082036479999999</v>
+        <v>7.98979104</v>
       </c>
       <c r="P10">
-        <v>18.85808512</v>
+        <v>18.64284576</v>
       </c>
       <c r="Q10">
-        <v>41.35808512</v>
+        <v>41.14284576</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07180472496487128</v>
+        <v>0.07200968023729301</v>
       </c>
       <c r="T10">
-        <v>0.6005710153549949</v>
+        <v>0.6053043934709704</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.9518103008669</v>
+        <v>10.62383137854836</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06879220901593665</v>
+        <v>0.06874227106419172</v>
       </c>
       <c r="C11">
-        <v>554.2819175716969</v>
+        <v>549.5424507095364</v>
       </c>
       <c r="D11">
-        <v>549.7059175716969</v>
+        <v>550.9024507095364</v>
       </c>
       <c r="E11">
-        <v>15.82400000000001</v>
+        <v>21.76000000000001</v>
       </c>
       <c r="F11">
-        <v>53.424</v>
+        <v>59.36</v>
       </c>
       <c r="G11">
         <v>58</v>
@@ -2177,45 +2177,45 @@
         <v>29.4</v>
       </c>
       <c r="M11">
-        <v>2.7673632</v>
+        <v>3.17576</v>
       </c>
       <c r="N11">
-        <v>26.6326368</v>
+        <v>26.22424</v>
       </c>
       <c r="O11">
-        <v>7.98979104</v>
+        <v>7.867271999999999</v>
       </c>
       <c r="P11">
-        <v>18.64284576</v>
+        <v>18.356968</v>
       </c>
       <c r="Q11">
-        <v>41.14284576</v>
+        <v>40.85696799999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07200968023729301</v>
+        <v>0.07221919007132413</v>
       </c>
       <c r="T11">
-        <v>0.6053043934709704</v>
+        <v>0.6101429577673012</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.62383137854836</v>
+        <v>9.257626520895785</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06874227106419172</v>
+        <v>0.06858523311244681</v>
       </c>
       <c r="C12">
-        <v>549.5424507095364</v>
+        <v>547.4033217814155</v>
       </c>
       <c r="D12">
-        <v>550.9024507095364</v>
+        <v>554.6993217814155</v>
       </c>
       <c r="E12">
-        <v>21.76000000000001</v>
+        <v>27.69600000000001</v>
       </c>
       <c r="F12">
-        <v>59.36000000000001</v>
+        <v>65.29600000000001</v>
       </c>
       <c r="G12">
         <v>58</v>
@@ -2259,28 +2259,28 @@
         <v>29.4</v>
       </c>
       <c r="M12">
-        <v>3.17576</v>
+        <v>3.493336</v>
       </c>
       <c r="N12">
-        <v>26.22424</v>
+        <v>25.906664</v>
       </c>
       <c r="O12">
-        <v>7.867271999999999</v>
+        <v>7.7719992</v>
       </c>
       <c r="P12">
-        <v>18.356968</v>
+        <v>18.1346648</v>
       </c>
       <c r="Q12">
-        <v>40.85696799999999</v>
+        <v>40.6346648</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07221919007132413</v>
+        <v>0.07243340799151327</v>
       </c>
       <c r="T12">
-        <v>0.6101429577673012</v>
+        <v>0.6150902538455719</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.257626520895784</v>
+        <v>8.416024109905258</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06858523311244681</v>
+        <v>0.06842819516070187</v>
       </c>
       <c r="C13">
-        <v>547.4033217814155</v>
+        <v>545.3168928456666</v>
       </c>
       <c r="D13">
-        <v>554.6993217814155</v>
+        <v>558.5488928456666</v>
       </c>
       <c r="E13">
-        <v>27.69600000000001</v>
+        <v>33.63200000000001</v>
       </c>
       <c r="F13">
-        <v>65.29600000000001</v>
+        <v>71.232</v>
       </c>
       <c r="G13">
         <v>58</v>
@@ -2341,28 +2341,28 @@
         <v>29.4</v>
       </c>
       <c r="M13">
-        <v>3.493336</v>
+        <v>3.810912</v>
       </c>
       <c r="N13">
-        <v>25.906664</v>
+        <v>25.589088</v>
       </c>
       <c r="O13">
-        <v>7.7719992</v>
+        <v>7.676726399999999</v>
       </c>
       <c r="P13">
-        <v>18.1346648</v>
+        <v>17.9123616</v>
       </c>
       <c r="Q13">
-        <v>40.6346648</v>
+        <v>40.4123616</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07243340799151327</v>
+        <v>0.07265249450079758</v>
       </c>
       <c r="T13">
-        <v>0.6150902538455719</v>
+        <v>0.6201499884710761</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.416024109905258</v>
+        <v>7.714688767413153</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06842819516070187</v>
+        <v>0.06834395720895695</v>
       </c>
       <c r="C14">
-        <v>545.3168928456666</v>
+        <v>541.467971624543</v>
       </c>
       <c r="D14">
-        <v>558.5488928456666</v>
+        <v>560.635971624543</v>
       </c>
       <c r="E14">
-        <v>33.63200000000001</v>
+        <v>39.56800000000001</v>
       </c>
       <c r="F14">
-        <v>71.232</v>
+        <v>77.16800000000001</v>
       </c>
       <c r="G14">
         <v>58</v>
@@ -2423,45 +2423,45 @@
         <v>29.4</v>
       </c>
       <c r="M14">
-        <v>3.810912</v>
+        <v>4.190222400000001</v>
       </c>
       <c r="N14">
-        <v>25.589088</v>
+        <v>25.2097776</v>
       </c>
       <c r="O14">
-        <v>7.676726399999999</v>
+        <v>7.562933279999999</v>
       </c>
       <c r="P14">
-        <v>17.9123616</v>
+        <v>17.64684432</v>
       </c>
       <c r="Q14">
-        <v>40.4123616</v>
+        <v>40.14684432</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07265249450079758</v>
+        <v>0.07287661748155971</v>
       </c>
       <c r="T14">
-        <v>0.6201499884710761</v>
+        <v>0.6253260388350975</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.714688767413153</v>
+        <v>7.016334025611623</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06834395720895695</v>
+        <v>0.06819251925721204</v>
       </c>
       <c r="C15">
-        <v>541.467971624543</v>
+        <v>539.323486203234</v>
       </c>
       <c r="D15">
-        <v>560.635971624543</v>
+        <v>564.427486203234</v>
       </c>
       <c r="E15">
-        <v>39.56800000000001</v>
+        <v>45.50400000000002</v>
       </c>
       <c r="F15">
-        <v>77.16800000000001</v>
+        <v>83.10400000000001</v>
       </c>
       <c r="G15">
         <v>58</v>
@@ -2505,28 +2505,28 @@
         <v>29.4</v>
       </c>
       <c r="M15">
-        <v>4.190222400000001</v>
+        <v>4.512547200000001</v>
       </c>
       <c r="N15">
-        <v>25.2097776</v>
+        <v>24.8874528</v>
       </c>
       <c r="O15">
-        <v>7.562933279999999</v>
+        <v>7.46623584</v>
       </c>
       <c r="P15">
-        <v>17.64684432</v>
+        <v>17.42121696</v>
       </c>
       <c r="Q15">
-        <v>40.14684432</v>
+        <v>39.92121696</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07287661748155971</v>
+        <v>0.07310595262466515</v>
       </c>
       <c r="T15">
-        <v>0.6253260388350975</v>
+        <v>0.6306224624633985</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.016334025611623</v>
+        <v>6.515167309496507</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06819251925721204</v>
+        <v>0.06814608130546712</v>
       </c>
       <c r="C16">
-        <v>539.323486203234</v>
+        <v>534.5604371116958</v>
       </c>
       <c r="D16">
-        <v>564.427486203234</v>
+        <v>565.6004371116959</v>
       </c>
       <c r="E16">
-        <v>45.50400000000002</v>
+        <v>51.44000000000003</v>
       </c>
       <c r="F16">
-        <v>83.10400000000001</v>
+        <v>89.04000000000002</v>
       </c>
       <c r="G16">
         <v>58</v>
@@ -2587,45 +2587,45 @@
         <v>29.4</v>
       </c>
       <c r="M16">
-        <v>4.512547200000001</v>
+        <v>4.923912000000001</v>
       </c>
       <c r="N16">
-        <v>24.8874528</v>
+        <v>24.476088</v>
       </c>
       <c r="O16">
-        <v>7.46623584</v>
+        <v>7.342826399999999</v>
       </c>
       <c r="P16">
-        <v>17.42121696</v>
+        <v>17.1332616</v>
       </c>
       <c r="Q16">
-        <v>39.92121696</v>
+        <v>39.6332616</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07310595262466515</v>
+        <v>0.07334068388878484</v>
       </c>
       <c r="T16">
-        <v>0.6306224624633985</v>
+        <v>0.6360435078241302</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.515167309496507</v>
+        <v>5.970862192500595</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06814608130546712</v>
+        <v>0.06800164335372219</v>
       </c>
       <c r="C17">
-        <v>534.5604371116959</v>
+        <v>532.3040822325943</v>
       </c>
       <c r="D17">
-        <v>565.6004371116959</v>
+        <v>569.2800822325943</v>
       </c>
       <c r="E17">
-        <v>51.44000000000001</v>
+        <v>57.376</v>
       </c>
       <c r="F17">
-        <v>89.04000000000001</v>
+        <v>94.976</v>
       </c>
       <c r="G17">
         <v>58</v>
@@ -2669,28 +2669,28 @@
         <v>29.4</v>
       </c>
       <c r="M17">
-        <v>4.923912000000001</v>
+        <v>5.2521728</v>
       </c>
       <c r="N17">
-        <v>24.476088</v>
+        <v>24.1478272</v>
       </c>
       <c r="O17">
-        <v>7.342826399999999</v>
+        <v>7.244348159999999</v>
       </c>
       <c r="P17">
-        <v>17.1332616</v>
+        <v>16.90347904</v>
       </c>
       <c r="Q17">
-        <v>39.6332616</v>
+        <v>39.40347904</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07334068388878484</v>
+        <v>0.07358100399252641</v>
       </c>
       <c r="T17">
-        <v>0.6360435078241302</v>
+        <v>0.6415936256934507</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.970862192500596</v>
+        <v>5.597683305469309</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06800164335372219</v>
+        <v>0.06785720540197726</v>
       </c>
       <c r="C18">
-        <v>532.3040822325943</v>
+        <v>530.095918445222</v>
       </c>
       <c r="D18">
-        <v>569.2800822325943</v>
+        <v>573.007918445222</v>
       </c>
       <c r="E18">
-        <v>57.376</v>
+        <v>63.31200000000001</v>
       </c>
       <c r="F18">
-        <v>94.976</v>
+        <v>100.912</v>
       </c>
       <c r="G18">
         <v>58</v>
@@ -2751,28 +2751,28 @@
         <v>29.4</v>
       </c>
       <c r="M18">
-        <v>5.2521728</v>
+        <v>5.5804336</v>
       </c>
       <c r="N18">
-        <v>24.1478272</v>
+        <v>23.8195664</v>
       </c>
       <c r="O18">
-        <v>7.244348159999999</v>
+        <v>7.14586992</v>
       </c>
       <c r="P18">
-        <v>16.90347904</v>
+        <v>16.67369648</v>
       </c>
       <c r="Q18">
-        <v>39.40347904</v>
+        <v>39.17369648</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07358100399252641</v>
+        <v>0.07382711494214128</v>
       </c>
       <c r="T18">
-        <v>0.6415936256934507</v>
+        <v>0.647277481342755</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.597683305469309</v>
+        <v>5.268407816912291</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06785720540197726</v>
+        <v>0.06771276745023233</v>
       </c>
       <c r="C19">
-        <v>530.095918445222</v>
+        <v>527.9368987039607</v>
       </c>
       <c r="D19">
-        <v>573.007918445222</v>
+        <v>576.7848987039606</v>
       </c>
       <c r="E19">
-        <v>63.31200000000001</v>
+        <v>69.24800000000002</v>
       </c>
       <c r="F19">
-        <v>100.912</v>
+        <v>106.848</v>
       </c>
       <c r="G19">
         <v>58</v>
@@ -2833,28 +2833,28 @@
         <v>29.4</v>
       </c>
       <c r="M19">
-        <v>5.5804336</v>
+        <v>5.908694400000001</v>
       </c>
       <c r="N19">
-        <v>23.8195664</v>
+        <v>23.4913056</v>
       </c>
       <c r="O19">
-        <v>7.14586992</v>
+        <v>7.047391679999999</v>
       </c>
       <c r="P19">
-        <v>16.67369648</v>
+        <v>16.44391392</v>
       </c>
       <c r="Q19">
-        <v>39.17369648</v>
+        <v>38.94391392</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07382711494214128</v>
+        <v>0.07407922859784431</v>
       </c>
       <c r="T19">
-        <v>0.647277481342755</v>
+        <v>0.6530999676176518</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.268407816912291</v>
+        <v>4.975718493750497</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06771276745023234</v>
+        <v>0.06756832949848741</v>
       </c>
       <c r="C20">
-        <v>527.9368987039601</v>
+        <v>525.8280012554902</v>
       </c>
       <c r="D20">
-        <v>576.78489870396</v>
+        <v>580.6120012554902</v>
       </c>
       <c r="E20">
-        <v>69.248</v>
+        <v>75.18400000000001</v>
       </c>
       <c r="F20">
-        <v>106.848</v>
+        <v>112.784</v>
       </c>
       <c r="G20">
         <v>58</v>
@@ -2915,28 +2915,28 @@
         <v>29.4</v>
       </c>
       <c r="M20">
-        <v>5.9086944</v>
+        <v>6.236955200000001</v>
       </c>
       <c r="N20">
-        <v>23.4913056</v>
+        <v>23.1630448</v>
       </c>
       <c r="O20">
-        <v>7.047391679999999</v>
+        <v>6.948913439999999</v>
       </c>
       <c r="P20">
-        <v>16.44391392</v>
+        <v>16.21413136</v>
       </c>
       <c r="Q20">
-        <v>38.94391392</v>
+        <v>38.71413136</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07407922859784431</v>
+        <v>0.07433756728208323</v>
       </c>
       <c r="T20">
-        <v>0.6530999676176518</v>
+        <v>0.659066218985756</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.975718493750497</v>
+        <v>4.713838573026786</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06756832949848741</v>
+        <v>0.0677738915467425</v>
       </c>
       <c r="C21">
-        <v>525.8280012554902</v>
+        <v>514.4604739374599</v>
       </c>
       <c r="D21">
-        <v>580.6120012554902</v>
+        <v>575.18047393746</v>
       </c>
       <c r="E21">
-        <v>75.18400000000001</v>
+        <v>81.12000000000002</v>
       </c>
       <c r="F21">
-        <v>112.784</v>
+        <v>118.72</v>
       </c>
       <c r="G21">
         <v>58</v>
@@ -2997,45 +2997,45 @@
         <v>29.4</v>
       </c>
       <c r="M21">
-        <v>6.236955200000001</v>
+        <v>6.862016000000001</v>
       </c>
       <c r="N21">
-        <v>23.1630448</v>
+        <v>22.537984</v>
       </c>
       <c r="O21">
-        <v>6.948913439999999</v>
+        <v>6.761395199999999</v>
       </c>
       <c r="P21">
-        <v>16.21413136</v>
+        <v>15.7765888</v>
       </c>
       <c r="Q21">
-        <v>38.71413136</v>
+        <v>38.2765888</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07433756728208323</v>
+        <v>0.07460236443342812</v>
       </c>
       <c r="T21">
-        <v>0.659066218985756</v>
+        <v>0.6651816266380629</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.713838573026786</v>
+        <v>4.284455180518377</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0677738915467425</v>
+        <v>0.06764695359499757</v>
       </c>
       <c r="C22">
-        <v>514.4604739374599</v>
+        <v>511.8664607699864</v>
       </c>
       <c r="D22">
-        <v>575.18047393746</v>
+        <v>578.5224607699864</v>
       </c>
       <c r="E22">
-        <v>81.12000000000002</v>
+        <v>87.05600000000003</v>
       </c>
       <c r="F22">
-        <v>118.72</v>
+        <v>124.656</v>
       </c>
       <c r="G22">
         <v>58</v>
@@ -3079,28 +3079,28 @@
         <v>29.4</v>
       </c>
       <c r="M22">
-        <v>6.862016000000001</v>
+        <v>7.205116800000002</v>
       </c>
       <c r="N22">
-        <v>22.537984</v>
+        <v>22.1948832</v>
       </c>
       <c r="O22">
-        <v>6.761395199999999</v>
+        <v>6.658464959999999</v>
       </c>
       <c r="P22">
-        <v>15.7765888</v>
+        <v>15.53641824</v>
       </c>
       <c r="Q22">
-        <v>38.2765888</v>
+        <v>38.03641824</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07460236443342812</v>
+        <v>0.07487386531012351</v>
       </c>
       <c r="T22">
-        <v>0.6651816266380629</v>
+        <v>0.6714518547372637</v>
       </c>
       <c r="U22">
         <v>0.0578</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.284455180518377</v>
+        <v>4.080433505255597</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06764695359499757</v>
+        <v>0.06805901564325265</v>
       </c>
       <c r="C23">
-        <v>511.8664607699864</v>
+        <v>495.2207710888658</v>
       </c>
       <c r="D23">
-        <v>578.5224607699864</v>
+        <v>567.8127710888658</v>
       </c>
       <c r="E23">
-        <v>87.05600000000001</v>
+        <v>92.99200000000002</v>
       </c>
       <c r="F23">
-        <v>124.656</v>
+        <v>130.592</v>
       </c>
       <c r="G23">
         <v>58</v>
@@ -3161,45 +3161,45 @@
         <v>29.4</v>
       </c>
       <c r="M23">
-        <v>7.205116800000001</v>
+        <v>8.005289600000001</v>
       </c>
       <c r="N23">
-        <v>22.1948832</v>
+        <v>21.3947104</v>
       </c>
       <c r="O23">
-        <v>6.65846496</v>
+        <v>6.418413119999999</v>
       </c>
       <c r="P23">
-        <v>15.53641824</v>
+        <v>14.97629728</v>
       </c>
       <c r="Q23">
-        <v>38.03641824</v>
+        <v>37.47629728</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07487386531012351</v>
+        <v>0.0751523277477598</v>
       </c>
       <c r="T23">
-        <v>0.6714518547372635</v>
+        <v>0.6778828579159309</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.080433505255598</v>
+        <v>3.672571695594872</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06805901564325265</v>
+        <v>0.06795657769150773</v>
       </c>
       <c r="C24">
-        <v>495.2207710888658</v>
+        <v>491.909976933144</v>
       </c>
       <c r="D24">
-        <v>567.8127710888658</v>
+        <v>570.437976933144</v>
       </c>
       <c r="E24">
-        <v>92.99200000000002</v>
+        <v>98.92800000000003</v>
       </c>
       <c r="F24">
-        <v>130.592</v>
+        <v>136.528</v>
       </c>
       <c r="G24">
         <v>58</v>
@@ -3243,28 +3243,28 @@
         <v>29.4</v>
       </c>
       <c r="M24">
-        <v>8.005289600000001</v>
+        <v>8.369166400000001</v>
       </c>
       <c r="N24">
-        <v>21.3947104</v>
+        <v>21.0308336</v>
       </c>
       <c r="O24">
-        <v>6.418413119999999</v>
+        <v>6.309250079999999</v>
       </c>
       <c r="P24">
-        <v>14.97629728</v>
+        <v>14.72158352</v>
       </c>
       <c r="Q24">
-        <v>37.47629728</v>
+        <v>37.22158352</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0751523277477598</v>
+        <v>0.07543802297598406</v>
       </c>
       <c r="T24">
-        <v>0.6778828579159309</v>
+        <v>0.6844809001382001</v>
       </c>
       <c r="U24">
         <v>0.0613</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.672571695594872</v>
+        <v>3.512894665351617</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06795657769150773</v>
+        <v>0.0683245397397628</v>
       </c>
       <c r="C25">
-        <v>491.909976933144</v>
+        <v>476.6552725858022</v>
       </c>
       <c r="D25">
-        <v>570.437976933144</v>
+        <v>561.1192725858023</v>
       </c>
       <c r="E25">
-        <v>98.92800000000003</v>
+        <v>104.864</v>
       </c>
       <c r="F25">
-        <v>136.528</v>
+        <v>142.464</v>
       </c>
       <c r="G25">
         <v>58</v>
@@ -3325,45 +3325,45 @@
         <v>29.4</v>
       </c>
       <c r="M25">
-        <v>8.369166400000001</v>
+        <v>9.131942400000002</v>
       </c>
       <c r="N25">
-        <v>21.0308336</v>
+        <v>20.2680576</v>
       </c>
       <c r="O25">
-        <v>6.309250079999999</v>
+        <v>6.08041728</v>
       </c>
       <c r="P25">
-        <v>14.72158352</v>
+        <v>14.18764032</v>
       </c>
       <c r="Q25">
-        <v>37.22158352</v>
+        <v>36.68764032</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07543802297598406</v>
+        <v>0.0757312364996879</v>
       </c>
       <c r="T25">
-        <v>0.6844809001382001</v>
+        <v>0.691252575050529</v>
       </c>
       <c r="U25">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.512894665351617</v>
+        <v>3.219468401377564</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0683245397397628</v>
+        <v>0.06824170178801789</v>
       </c>
       <c r="C26">
-        <v>476.6552725858023</v>
+        <v>472.7905046013003</v>
       </c>
       <c r="D26">
-        <v>561.1192725858023</v>
+        <v>563.1905046013003</v>
       </c>
       <c r="E26">
-        <v>104.864</v>
+        <v>110.8</v>
       </c>
       <c r="F26">
-        <v>142.464</v>
+        <v>148.4</v>
       </c>
       <c r="G26">
         <v>58</v>
@@ -3407,28 +3407,28 @@
         <v>29.4</v>
       </c>
       <c r="M26">
-        <v>9.1319424</v>
+        <v>9.512440000000002</v>
       </c>
       <c r="N26">
-        <v>20.2680576</v>
+        <v>19.88756</v>
       </c>
       <c r="O26">
-        <v>6.08041728</v>
+        <v>5.966267999999999</v>
       </c>
       <c r="P26">
-        <v>14.18764032</v>
+        <v>13.921292</v>
       </c>
       <c r="Q26">
-        <v>36.68764032</v>
+        <v>36.42129199999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0757312364996879</v>
+        <v>0.07603226905069051</v>
       </c>
       <c r="T26">
-        <v>0.691252575050529</v>
+        <v>0.69820482796052</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.219468401377565</v>
+        <v>3.090689665322461</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06824170178801789</v>
+        <v>0.06957846383627295</v>
       </c>
       <c r="C27">
-        <v>472.7905046013003</v>
+        <v>435.1934310486769</v>
       </c>
       <c r="D27">
-        <v>563.1905046013003</v>
+        <v>531.5294310486769</v>
       </c>
       <c r="E27">
-        <v>110.8</v>
+        <v>116.736</v>
       </c>
       <c r="F27">
-        <v>148.4</v>
+        <v>154.336</v>
       </c>
       <c r="G27">
         <v>58</v>
@@ -3489,45 +3489,45 @@
         <v>29.4</v>
       </c>
       <c r="M27">
-        <v>9.512440000000002</v>
+        <v>11.0967584</v>
       </c>
       <c r="N27">
-        <v>19.88756</v>
+        <v>18.3032416</v>
       </c>
       <c r="O27">
-        <v>5.966267999999999</v>
+        <v>5.490972479999999</v>
       </c>
       <c r="P27">
-        <v>13.921292</v>
+        <v>12.81226912</v>
       </c>
       <c r="Q27">
-        <v>36.42129199999999</v>
+        <v>35.31226912</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07603226905069051</v>
+        <v>0.07634143761658507</v>
       </c>
       <c r="T27">
-        <v>0.69820482796052</v>
+        <v>0.7053449795978078</v>
       </c>
       <c r="U27">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.090689665322461</v>
+        <v>2.649422375456962</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06957846383627295</v>
+        <v>0.06955022588452804</v>
       </c>
       <c r="C28">
-        <v>435.1934310486769</v>
+        <v>429.8893956665261</v>
       </c>
       <c r="D28">
-        <v>531.5294310486769</v>
+        <v>532.1613956665261</v>
       </c>
       <c r="E28">
-        <v>116.736</v>
+        <v>122.672</v>
       </c>
       <c r="F28">
-        <v>154.336</v>
+        <v>160.272</v>
       </c>
       <c r="G28">
         <v>58</v>
@@ -3571,28 +3571,28 @@
         <v>29.4</v>
       </c>
       <c r="M28">
-        <v>11.0967584</v>
+        <v>11.5235568</v>
       </c>
       <c r="N28">
-        <v>18.3032416</v>
+        <v>17.8764432</v>
       </c>
       <c r="O28">
-        <v>5.490972479999999</v>
+        <v>5.362932959999999</v>
       </c>
       <c r="P28">
-        <v>12.81226912</v>
+        <v>12.51351024</v>
       </c>
       <c r="Q28">
-        <v>35.31226912</v>
+        <v>35.01351024</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07634143761658507</v>
+        <v>0.076659076554148</v>
       </c>
       <c r="T28">
-        <v>0.7053449795978078</v>
+        <v>0.7126807518278984</v>
       </c>
       <c r="U28">
         <v>0.07190000000000001</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.649422375456962</v>
+        <v>2.551295620810408</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06955022588452804</v>
+        <v>0.07028638793278311</v>
       </c>
       <c r="C29">
-        <v>429.8893956665261</v>
+        <v>407.9544241517586</v>
       </c>
       <c r="D29">
-        <v>532.1613956665261</v>
+        <v>516.1624241517586</v>
       </c>
       <c r="E29">
-        <v>122.672</v>
+        <v>128.608</v>
       </c>
       <c r="F29">
-        <v>160.272</v>
+        <v>166.208</v>
       </c>
       <c r="G29">
         <v>58</v>
@@ -3653,45 +3653,45 @@
         <v>29.4</v>
       </c>
       <c r="M29">
-        <v>11.5235568</v>
+        <v>12.5985664</v>
       </c>
       <c r="N29">
-        <v>17.8764432</v>
+        <v>16.8014336</v>
       </c>
       <c r="O29">
-        <v>5.362932959999999</v>
+        <v>5.040430079999998</v>
       </c>
       <c r="P29">
-        <v>12.51351024</v>
+        <v>11.76100352</v>
       </c>
       <c r="Q29">
-        <v>35.01351024</v>
+        <v>34.26100352</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.076659076554148</v>
+        <v>0.0769855387955321</v>
       </c>
       <c r="T29">
-        <v>0.7126807518278984</v>
+        <v>0.7202202955088246</v>
       </c>
       <c r="U29">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.551295620810408</v>
+        <v>2.333598845024144</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07028638793278311</v>
+        <v>0.07028544998103819</v>
       </c>
       <c r="C30">
-        <v>407.9544241517586</v>
+        <v>402.0381965246072</v>
       </c>
       <c r="D30">
-        <v>516.1624241517586</v>
+        <v>516.1821965246072</v>
       </c>
       <c r="E30">
-        <v>128.608</v>
+        <v>134.544</v>
       </c>
       <c r="F30">
-        <v>166.208</v>
+        <v>172.144</v>
       </c>
       <c r="G30">
         <v>58</v>
@@ -3735,28 +3735,28 @@
         <v>29.4</v>
       </c>
       <c r="M30">
-        <v>12.5985664</v>
+        <v>13.0485152</v>
       </c>
       <c r="N30">
-        <v>16.8014336</v>
+        <v>16.35148479999999</v>
       </c>
       <c r="O30">
-        <v>5.040430079999998</v>
+        <v>4.905445439999998</v>
       </c>
       <c r="P30">
-        <v>11.76100352</v>
+        <v>11.44603936</v>
       </c>
       <c r="Q30">
-        <v>34.26100352</v>
+        <v>33.94603936</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0769855387955321</v>
+        <v>0.07732119715639182</v>
       </c>
       <c r="T30">
-        <v>0.7202202955088246</v>
+        <v>0.7279722207018897</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.333598845024144</v>
+        <v>2.253129919333657</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07028544998103819</v>
+        <v>0.07028451202929327</v>
       </c>
       <c r="C31">
-        <v>402.0381965246072</v>
+        <v>396.1219704123347</v>
       </c>
       <c r="D31">
-        <v>516.1821965246072</v>
+        <v>516.2019704123347</v>
       </c>
       <c r="E31">
-        <v>134.544</v>
+        <v>140.48</v>
       </c>
       <c r="F31">
-        <v>172.144</v>
+        <v>178.08</v>
       </c>
       <c r="G31">
         <v>58</v>
@@ -3817,28 +3817,28 @@
         <v>29.4</v>
       </c>
       <c r="M31">
-        <v>13.0485152</v>
+        <v>13.498464</v>
       </c>
       <c r="N31">
-        <v>16.3514848</v>
+        <v>15.901536</v>
       </c>
       <c r="O31">
-        <v>4.905445439999999</v>
+        <v>4.770460799999999</v>
       </c>
       <c r="P31">
-        <v>11.44603936</v>
+        <v>11.1310752</v>
       </c>
       <c r="Q31">
-        <v>33.94603936</v>
+        <v>33.6310752</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07732119715639182</v>
+        <v>0.07766644575613324</v>
       </c>
       <c r="T31">
-        <v>0.7279722207018897</v>
+        <v>0.7359456294718995</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.253129919333657</v>
+        <v>2.178025588689201</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07028451202929327</v>
+        <v>0.07028357407754834</v>
       </c>
       <c r="C32">
-        <v>396.1219704123347</v>
+        <v>390.2057458151149</v>
       </c>
       <c r="D32">
-        <v>516.2019704123347</v>
+        <v>516.2217458151149</v>
       </c>
       <c r="E32">
-        <v>140.48</v>
+        <v>146.416</v>
       </c>
       <c r="F32">
-        <v>178.08</v>
+        <v>184.016</v>
       </c>
       <c r="G32">
         <v>58</v>
@@ -3899,28 +3899,28 @@
         <v>29.4</v>
       </c>
       <c r="M32">
-        <v>13.498464</v>
+        <v>13.9484128</v>
       </c>
       <c r="N32">
-        <v>15.901536</v>
+        <v>15.4515872</v>
       </c>
       <c r="O32">
-        <v>4.770460799999999</v>
+        <v>4.635476159999999</v>
       </c>
       <c r="P32">
-        <v>11.1310752</v>
+        <v>10.81611104</v>
       </c>
       <c r="Q32">
-        <v>33.6310752</v>
+        <v>33.31611104</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07766644575613324</v>
+        <v>0.07802170156166427</v>
       </c>
       <c r="T32">
-        <v>0.7359456294718995</v>
+        <v>0.7441501515395905</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.178025588689201</v>
+        <v>2.107766698731485</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07028357407754834</v>
+        <v>0.07028263612580342</v>
       </c>
       <c r="C33">
-        <v>390.2057458151149</v>
+        <v>384.2895227331219</v>
       </c>
       <c r="D33">
-        <v>516.2217458151149</v>
+        <v>516.2415227331219</v>
       </c>
       <c r="E33">
-        <v>146.416</v>
+        <v>152.352</v>
       </c>
       <c r="F33">
-        <v>184.016</v>
+        <v>189.952</v>
       </c>
       <c r="G33">
         <v>58</v>
@@ -3981,28 +3981,28 @@
         <v>29.4</v>
       </c>
       <c r="M33">
-        <v>13.9484128</v>
+        <v>14.3983616</v>
       </c>
       <c r="N33">
-        <v>15.4515872</v>
+        <v>15.0016384</v>
       </c>
       <c r="O33">
-        <v>4.635476159999999</v>
+        <v>4.500491519999999</v>
       </c>
       <c r="P33">
-        <v>10.81611104</v>
+        <v>10.50114688</v>
       </c>
       <c r="Q33">
-        <v>33.31611104</v>
+        <v>33.00114688</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07802170156166427</v>
+        <v>0.07838740606735797</v>
       </c>
       <c r="T33">
-        <v>0.7441501515395905</v>
+        <v>0.7525959830798609</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.107766698731485</v>
+        <v>2.041898989396127</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07028263612580342</v>
+        <v>0.07356189817405849</v>
       </c>
       <c r="C34">
-        <v>384.2895227331219</v>
+        <v>317.3745787640088</v>
       </c>
       <c r="D34">
-        <v>516.2415227331219</v>
+        <v>455.2625787640089</v>
       </c>
       <c r="E34">
-        <v>152.352</v>
+        <v>158.288</v>
       </c>
       <c r="F34">
-        <v>189.952</v>
+        <v>195.888</v>
       </c>
       <c r="G34">
         <v>58</v>
@@ -4063,45 +4063,45 @@
         <v>29.4</v>
       </c>
       <c r="M34">
-        <v>14.3983616</v>
+        <v>17.62992</v>
       </c>
       <c r="N34">
-        <v>15.0016384</v>
+        <v>11.77008</v>
       </c>
       <c r="O34">
-        <v>4.500491519999999</v>
+        <v>3.531024</v>
       </c>
       <c r="P34">
-        <v>10.50114688</v>
+        <v>8.239056</v>
       </c>
       <c r="Q34">
-        <v>33.00114688</v>
+        <v>30.739056</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07838740606735797</v>
+        <v>0.07876402712546045</v>
       </c>
       <c r="T34">
-        <v>0.7525959830798609</v>
+        <v>0.7612939289944678</v>
       </c>
       <c r="U34">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.041898989396127</v>
+        <v>1.667619592147894</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07356189817405849</v>
+        <v>0.07366036022231356</v>
       </c>
       <c r="C35">
-        <v>317.3745787640088</v>
+        <v>309.8296230419257</v>
       </c>
       <c r="D35">
-        <v>455.2625787640089</v>
+        <v>453.6536230419257</v>
       </c>
       <c r="E35">
-        <v>158.288</v>
+        <v>164.224</v>
       </c>
       <c r="F35">
-        <v>195.888</v>
+        <v>201.824</v>
       </c>
       <c r="G35">
         <v>58</v>
@@ -4145,28 +4145,28 @@
         <v>29.4</v>
       </c>
       <c r="M35">
-        <v>17.62992</v>
+        <v>18.16416</v>
       </c>
       <c r="N35">
-        <v>11.77008</v>
+        <v>11.23584</v>
       </c>
       <c r="O35">
-        <v>3.531024</v>
+        <v>3.370752</v>
       </c>
       <c r="P35">
-        <v>8.239056</v>
+        <v>7.865088</v>
       </c>
       <c r="Q35">
-        <v>30.739056</v>
+        <v>30.365088</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07876402712546045</v>
+        <v>0.07915206094289935</v>
       </c>
       <c r="T35">
-        <v>0.7612939289944678</v>
+        <v>0.7702554490276988</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.667619592147894</v>
+        <v>1.618571957084721</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07366036022231356</v>
+        <v>0.07375882227056865</v>
       </c>
       <c r="C36">
-        <v>309.8296230419257</v>
+        <v>302.2959997768688</v>
       </c>
       <c r="D36">
-        <v>453.6536230419257</v>
+        <v>452.0559997768688</v>
       </c>
       <c r="E36">
-        <v>164.224</v>
+        <v>170.16</v>
       </c>
       <c r="F36">
-        <v>201.824</v>
+        <v>207.76</v>
       </c>
       <c r="G36">
         <v>58</v>
@@ -4227,28 +4227,28 @@
         <v>29.4</v>
       </c>
       <c r="M36">
-        <v>18.16416</v>
+        <v>18.6984</v>
       </c>
       <c r="N36">
-        <v>11.23584</v>
+        <v>10.7016</v>
       </c>
       <c r="O36">
-        <v>3.370752</v>
+        <v>3.21048</v>
       </c>
       <c r="P36">
-        <v>7.865088</v>
+        <v>7.49112</v>
       </c>
       <c r="Q36">
-        <v>30.365088</v>
+        <v>29.99112</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07915206094289935</v>
+        <v>0.07955203426241331</v>
       </c>
       <c r="T36">
-        <v>0.7702554490276988</v>
+        <v>0.7794927081388756</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.618571957084721</v>
+        <v>1.572327044025157</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07375882227056865</v>
+        <v>0.07385728431882373</v>
       </c>
       <c r="C37">
-        <v>302.2959997768688</v>
+        <v>294.7735896611128</v>
       </c>
       <c r="D37">
-        <v>452.0559997768688</v>
+        <v>450.4695896611128</v>
       </c>
       <c r="E37">
-        <v>170.16</v>
+        <v>176.096</v>
       </c>
       <c r="F37">
-        <v>207.76</v>
+        <v>213.696</v>
       </c>
       <c r="G37">
         <v>58</v>
@@ -4309,28 +4309,28 @@
         <v>29.4</v>
       </c>
       <c r="M37">
-        <v>18.6984</v>
+        <v>19.23264</v>
       </c>
       <c r="N37">
-        <v>10.7016</v>
+        <v>10.16736</v>
       </c>
       <c r="O37">
-        <v>3.21048</v>
+        <v>3.050208</v>
       </c>
       <c r="P37">
-        <v>7.49112</v>
+        <v>7.117151999999999</v>
       </c>
       <c r="Q37">
-        <v>29.99112</v>
+        <v>29.617152</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07955203426241331</v>
+        <v>0.07996450674816208</v>
       </c>
       <c r="T37">
-        <v>0.7794927081388756</v>
+        <v>0.7890186315972768</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.572327044025157</v>
+        <v>1.528651292802236</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07385728431882374</v>
+        <v>0.0903430906190372</v>
       </c>
       <c r="C38">
-        <v>294.7735896611125</v>
+        <v>122.1146637015069</v>
       </c>
       <c r="D38">
-        <v>450.4695896611125</v>
+        <v>283.7466637015069</v>
       </c>
       <c r="E38">
-        <v>176.096</v>
+        <v>182.032</v>
       </c>
       <c r="F38">
-        <v>213.696</v>
+        <v>219.632</v>
       </c>
       <c r="G38">
         <v>58</v>
@@ -4391,45 +4391,45 @@
         <v>29.4</v>
       </c>
       <c r="M38">
-        <v>19.23264</v>
+        <v>32.24197760000001</v>
       </c>
       <c r="N38">
-        <v>10.16736</v>
+        <v>-2.841977600000007</v>
       </c>
       <c r="O38">
-        <v>3.050208</v>
+        <v>-0.8525932800000021</v>
       </c>
       <c r="P38">
-        <v>7.117151999999999</v>
+        <v>-1.989384320000005</v>
       </c>
       <c r="Q38">
-        <v>29.617152</v>
+        <v>20.51061567999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07996450674816208</v>
+        <v>0.08077076378583323</v>
       </c>
       <c r="T38">
-        <v>0.7890186315972768</v>
+        <v>0.8076388865088507</v>
       </c>
       <c r="U38">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.3</v>
+        <v>0.2735564210552642</v>
       </c>
       <c r="W38">
-        <v>0.063</v>
+        <v>0.1066419173890872</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>1.528651292802236</v>
+        <v>0.9118547368508808</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0903430906190372</v>
+        <v>0.09135309061903721</v>
       </c>
       <c r="C39">
-        <v>122.1146637015069</v>
+        <v>109.8874521405781</v>
       </c>
       <c r="D39">
-        <v>283.7466637015069</v>
+        <v>277.4554521405781</v>
       </c>
       <c r="E39">
-        <v>182.032</v>
+        <v>187.968</v>
       </c>
       <c r="F39">
-        <v>219.632</v>
+        <v>225.568</v>
       </c>
       <c r="G39">
         <v>58</v>
@@ -4473,37 +4473,37 @@
         <v>29.4</v>
       </c>
       <c r="M39">
-        <v>32.24197760000001</v>
+        <v>33.11338240000001</v>
       </c>
       <c r="N39">
-        <v>-2.841977600000007</v>
+        <v>-3.713382400000008</v>
       </c>
       <c r="O39">
-        <v>-0.8525932800000021</v>
+        <v>-1.114014720000002</v>
       </c>
       <c r="P39">
-        <v>-1.989384320000005</v>
+        <v>-2.599367680000006</v>
       </c>
       <c r="Q39">
-        <v>20.51061567999999</v>
+        <v>19.90063231999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08077076378583323</v>
+        <v>0.08133480836302409</v>
       </c>
       <c r="T39">
-        <v>0.8076388865088507</v>
+        <v>0.8206653201622193</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.2735564210552642</v>
+        <v>0.2663575678695994</v>
       </c>
       <c r="W39">
-        <v>0.1066419173890872</v>
+        <v>0.1076987090367428</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.9118547368508808</v>
+        <v>0.8878585595653313</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09135309061903721</v>
+        <v>0.09236309061903721</v>
       </c>
       <c r="C40">
-        <v>109.8874521405781</v>
+        <v>97.93316591995921</v>
       </c>
       <c r="D40">
-        <v>277.4554521405781</v>
+        <v>271.4371659199592</v>
       </c>
       <c r="E40">
-        <v>187.968</v>
+        <v>193.904</v>
       </c>
       <c r="F40">
-        <v>225.568</v>
+        <v>231.504</v>
       </c>
       <c r="G40">
         <v>58</v>
@@ -4555,37 +4555,37 @@
         <v>29.4</v>
       </c>
       <c r="M40">
-        <v>33.11338240000001</v>
+        <v>33.98478720000001</v>
       </c>
       <c r="N40">
-        <v>-3.713382400000008</v>
+        <v>-4.584787200000008</v>
       </c>
       <c r="O40">
-        <v>-1.114014720000002</v>
+        <v>-1.375436160000002</v>
       </c>
       <c r="P40">
-        <v>-2.599367680000006</v>
+        <v>-3.209351040000006</v>
       </c>
       <c r="Q40">
-        <v>19.90063231999999</v>
+        <v>19.29064896</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08133480836302409</v>
+        <v>0.08191734620504088</v>
       </c>
       <c r="T40">
-        <v>0.8206653201622193</v>
+        <v>0.8341188500009442</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.2663575678695994</v>
+        <v>0.2595278866421737</v>
       </c>
       <c r="W40">
-        <v>0.1076987090367428</v>
+        <v>0.1087013062409289</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8878585595653313</v>
+        <v>0.8650929554739125</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09236309061903721</v>
+        <v>0.0933730906190372</v>
       </c>
       <c r="C41">
-        <v>97.93316591995921</v>
+        <v>86.2344220239498</v>
       </c>
       <c r="D41">
-        <v>271.4371659199592</v>
+        <v>265.6744220239498</v>
       </c>
       <c r="E41">
-        <v>193.904</v>
+        <v>199.84</v>
       </c>
       <c r="F41">
-        <v>231.504</v>
+        <v>237.44</v>
       </c>
       <c r="G41">
         <v>58</v>
@@ -4637,37 +4637,37 @@
         <v>29.4</v>
       </c>
       <c r="M41">
-        <v>33.98478720000001</v>
+        <v>34.85619200000001</v>
       </c>
       <c r="N41">
-        <v>-4.584787200000008</v>
+        <v>-5.456192000000009</v>
       </c>
       <c r="O41">
-        <v>-1.375436160000002</v>
+        <v>-1.636857600000003</v>
       </c>
       <c r="P41">
-        <v>-3.209351040000006</v>
+        <v>-3.819334400000006</v>
       </c>
       <c r="Q41">
-        <v>19.29064896</v>
+        <v>18.68066559999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08191734620504088</v>
+        <v>0.08251930197512489</v>
       </c>
       <c r="T41">
-        <v>0.8341188500009442</v>
+        <v>0.8480208308342932</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.2595278866421737</v>
+        <v>0.2530396894761194</v>
       </c>
       <c r="W41">
-        <v>0.1087013062409289</v>
+        <v>0.1096537735849057</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8650929554739125</v>
+        <v>0.8434656315870648</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0933730906190372</v>
+        <v>0.09438309061903721</v>
       </c>
       <c r="C42">
-        <v>86.2344220239498</v>
+        <v>74.77528294767524</v>
       </c>
       <c r="D42">
-        <v>265.6744220239498</v>
+        <v>260.1512829476753</v>
       </c>
       <c r="E42">
-        <v>199.84</v>
+        <v>205.776</v>
       </c>
       <c r="F42">
-        <v>237.44</v>
+        <v>243.376</v>
       </c>
       <c r="G42">
         <v>58</v>
@@ -4719,37 +4719,37 @@
         <v>29.4</v>
       </c>
       <c r="M42">
-        <v>34.85619200000001</v>
+        <v>35.72759680000001</v>
       </c>
       <c r="N42">
-        <v>-5.456192000000009</v>
+        <v>-6.327596800000009</v>
       </c>
       <c r="O42">
-        <v>-1.636857600000003</v>
+        <v>-1.898279040000003</v>
       </c>
       <c r="P42">
-        <v>-3.819334400000006</v>
+        <v>-4.429317760000006</v>
       </c>
       <c r="Q42">
-        <v>18.68066559999999</v>
+        <v>18.07068223999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08251930197512489</v>
+        <v>0.08314166302555073</v>
       </c>
       <c r="T42">
-        <v>0.8480208308342932</v>
+        <v>0.8623940652552133</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2530396894761194</v>
+        <v>0.2468679897327994</v>
       </c>
       <c r="W42">
-        <v>0.1096537735849057</v>
+        <v>0.1105597791072251</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8434656315870648</v>
+        <v>0.8228932991093314</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09438309061903721</v>
+        <v>0.0953930906190372</v>
       </c>
       <c r="C43">
-        <v>74.77528294767524</v>
+        <v>63.54110950259687</v>
       </c>
       <c r="D43">
-        <v>260.1512829476753</v>
+        <v>254.8531095025969</v>
       </c>
       <c r="E43">
-        <v>205.776</v>
+        <v>211.712</v>
       </c>
       <c r="F43">
-        <v>243.376</v>
+        <v>249.312</v>
       </c>
       <c r="G43">
         <v>58</v>
@@ -4801,37 +4801,37 @@
         <v>29.4</v>
       </c>
       <c r="M43">
-        <v>35.72759680000001</v>
+        <v>36.59900160000001</v>
       </c>
       <c r="N43">
-        <v>-6.327596800000009</v>
+        <v>-7.19900160000001</v>
       </c>
       <c r="O43">
-        <v>-1.898279040000003</v>
+        <v>-2.159700480000003</v>
       </c>
       <c r="P43">
-        <v>-4.429317760000006</v>
+        <v>-5.039301120000006</v>
       </c>
       <c r="Q43">
-        <v>18.07068223999999</v>
+        <v>17.46069888</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08314166302555073</v>
+        <v>0.08378548480185333</v>
       </c>
       <c r="T43">
-        <v>0.8623940652552133</v>
+        <v>0.8772629284492688</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.2468679897327994</v>
+        <v>0.2409901804534471</v>
       </c>
       <c r="W43">
-        <v>0.1105597791072251</v>
+        <v>0.111422641509434</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8228932991093314</v>
+        <v>0.8033006015114902</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0953930906190372</v>
+        <v>0.1202903104766795</v>
       </c>
       <c r="C44">
-        <v>63.5411095025969</v>
+        <v>-27.57555168791316</v>
       </c>
       <c r="D44">
-        <v>254.8531095025969</v>
+        <v>169.6724483120869</v>
       </c>
       <c r="E44">
-        <v>211.712</v>
+        <v>217.648</v>
       </c>
       <c r="F44">
-        <v>249.312</v>
+        <v>255.248</v>
       </c>
       <c r="G44">
         <v>58</v>
@@ -4883,45 +4883,45 @@
         <v>29.4</v>
       </c>
       <c r="M44">
-        <v>36.59900160000001</v>
+        <v>51.25379840000001</v>
       </c>
       <c r="N44">
-        <v>-7.19900160000001</v>
+        <v>-21.85379840000001</v>
       </c>
       <c r="O44">
-        <v>-2.159700480000003</v>
+        <v>-6.556139520000003</v>
       </c>
       <c r="P44">
-        <v>-5.039301120000006</v>
+        <v>-15.29765888000001</v>
       </c>
       <c r="Q44">
-        <v>17.46069888</v>
+        <v>7.202341119999993</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08378548480185333</v>
+        <v>0.08562245796967928</v>
       </c>
       <c r="T44">
-        <v>0.8772629284492688</v>
+        <v>0.9196872510318542</v>
       </c>
       <c r="U44">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.2409901804534471</v>
+        <v>0.1720848068891612</v>
       </c>
       <c r="W44">
-        <v>0.111422641509434</v>
+        <v>0.1662453707766564</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.8033006015114902</v>
+        <v>0.5736160229638706</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1202903104766795</v>
+        <v>0.1218403104766795</v>
       </c>
       <c r="C45">
-        <v>-27.57555168791316</v>
+        <v>-36.97014218070703</v>
       </c>
       <c r="D45">
-        <v>169.6724483120869</v>
+        <v>166.213857819293</v>
       </c>
       <c r="E45">
-        <v>217.648</v>
+        <v>223.584</v>
       </c>
       <c r="F45">
-        <v>255.248</v>
+        <v>261.184</v>
       </c>
       <c r="G45">
         <v>58</v>
@@ -4965,37 +4965,37 @@
         <v>29.4</v>
       </c>
       <c r="M45">
-        <v>51.25379840000001</v>
+        <v>52.44574720000001</v>
       </c>
       <c r="N45">
-        <v>-21.85379840000001</v>
+        <v>-23.04574720000001</v>
       </c>
       <c r="O45">
-        <v>-6.556139520000003</v>
+        <v>-6.913724160000002</v>
       </c>
       <c r="P45">
-        <v>-15.29765888000001</v>
+        <v>-16.13202304000001</v>
       </c>
       <c r="Q45">
-        <v>7.202341119999993</v>
+        <v>6.367976959999993</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08562245796967928</v>
+        <v>0.0863335732905664</v>
       </c>
       <c r="T45">
-        <v>0.9196872510318542</v>
+        <v>0.936110237657423</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1720848068891612</v>
+        <v>0.1681737885507712</v>
       </c>
       <c r="W45">
-        <v>0.1662453707766564</v>
+        <v>0.1670307032590052</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5736160229638706</v>
+        <v>0.5605792951692372</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1218403104766795</v>
+        <v>0.1233903104766795</v>
       </c>
       <c r="C46">
-        <v>-36.97014218070703</v>
+        <v>-46.22655007748094</v>
       </c>
       <c r="D46">
-        <v>166.213857819293</v>
+        <v>162.8934499225191</v>
       </c>
       <c r="E46">
-        <v>223.584</v>
+        <v>229.52</v>
       </c>
       <c r="F46">
-        <v>261.184</v>
+        <v>267.12</v>
       </c>
       <c r="G46">
         <v>58</v>
@@ -5047,37 +5047,37 @@
         <v>29.4</v>
       </c>
       <c r="M46">
-        <v>52.44574720000001</v>
+        <v>53.63769600000001</v>
       </c>
       <c r="N46">
-        <v>-23.04574720000001</v>
+        <v>-24.23769600000001</v>
       </c>
       <c r="O46">
-        <v>-6.913724160000002</v>
+        <v>-7.271308800000002</v>
       </c>
       <c r="P46">
-        <v>-16.13202304000001</v>
+        <v>-16.96638720000001</v>
       </c>
       <c r="Q46">
-        <v>6.367976959999993</v>
+        <v>5.533612799999993</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0863335732905664</v>
+        <v>0.08707054735039489</v>
       </c>
       <c r="T46">
-        <v>0.936110237657423</v>
+        <v>0.9531304237966489</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1681737885507712</v>
+        <v>0.1644365932496429</v>
       </c>
       <c r="W46">
-        <v>0.1670307032590052</v>
+        <v>0.1677811320754717</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5605792951692372</v>
+        <v>0.5481219774988098</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1233903104766795</v>
+        <v>0.1249403104766795</v>
       </c>
       <c r="C47">
-        <v>-46.22655007748094</v>
+        <v>-55.3528944905762</v>
       </c>
       <c r="D47">
-        <v>162.8934499225191</v>
+        <v>159.7031055094238</v>
       </c>
       <c r="E47">
-        <v>229.52</v>
+        <v>235.456</v>
       </c>
       <c r="F47">
-        <v>267.12</v>
+        <v>273.056</v>
       </c>
       <c r="G47">
         <v>58</v>
@@ -5129,37 +5129,37 @@
         <v>29.4</v>
       </c>
       <c r="M47">
-        <v>53.63769600000001</v>
+        <v>54.82964480000001</v>
       </c>
       <c r="N47">
-        <v>-24.23769600000001</v>
+        <v>-25.42964480000001</v>
       </c>
       <c r="O47">
-        <v>-7.271308800000002</v>
+        <v>-7.628893440000003</v>
       </c>
       <c r="P47">
-        <v>-16.96638720000001</v>
+        <v>-17.80075136000001</v>
       </c>
       <c r="Q47">
-        <v>5.533612799999993</v>
+        <v>4.69924863999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08707054735039489</v>
+        <v>0.08783481674577256</v>
       </c>
       <c r="T47">
-        <v>0.9531304237966489</v>
+        <v>0.9707809872002905</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1644365932496429</v>
+        <v>0.1608618847007376</v>
       </c>
       <c r="W47">
-        <v>0.1677811320754717</v>
+        <v>0.1684989335520919</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5481219774988098</v>
+        <v>0.536206282335792</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1249403104766795</v>
+        <v>0.1264903104766795</v>
       </c>
       <c r="C48">
-        <v>-55.3528944905762</v>
+        <v>-64.35667068423891</v>
       </c>
       <c r="D48">
-        <v>159.7031055094238</v>
+        <v>156.6353293157611</v>
       </c>
       <c r="E48">
-        <v>235.456</v>
+        <v>241.392</v>
       </c>
       <c r="F48">
-        <v>273.056</v>
+        <v>278.992</v>
       </c>
       <c r="G48">
         <v>58</v>
@@ -5211,37 +5211,37 @@
         <v>29.4</v>
       </c>
       <c r="M48">
-        <v>54.82964480000001</v>
+        <v>56.0215936</v>
       </c>
       <c r="N48">
-        <v>-25.42964480000001</v>
+        <v>-26.6215936</v>
       </c>
       <c r="O48">
-        <v>-7.628893440000003</v>
+        <v>-7.986478080000001</v>
       </c>
       <c r="P48">
-        <v>-17.80075136000001</v>
+        <v>-18.63511552</v>
       </c>
       <c r="Q48">
-        <v>4.69924863999999</v>
+        <v>3.864884479999997</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08783481674577256</v>
+        <v>0.08862792649569282</v>
       </c>
       <c r="T48">
-        <v>0.9707809872002905</v>
+        <v>0.989097609600296</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1608618847007376</v>
+        <v>0.1574392914092326</v>
       </c>
       <c r="W48">
-        <v>0.1684989335520919</v>
+        <v>0.1691861902850261</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.536206282335792</v>
+        <v>0.5247976380307753</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1264903104766795</v>
+        <v>0.1280403104766795</v>
       </c>
       <c r="C49">
-        <v>-64.35667068423891</v>
+        <v>-73.24480886358441</v>
       </c>
       <c r="D49">
-        <v>156.6353293157611</v>
+        <v>153.6831911364156</v>
       </c>
       <c r="E49">
-        <v>241.392</v>
+        <v>247.3280000000001</v>
       </c>
       <c r="F49">
-        <v>278.992</v>
+        <v>284.9280000000001</v>
       </c>
       <c r="G49">
         <v>58</v>
@@ -5293,37 +5293,37 @@
         <v>29.4</v>
       </c>
       <c r="M49">
-        <v>56.0215936</v>
+        <v>57.21354240000002</v>
       </c>
       <c r="N49">
-        <v>-26.6215936</v>
+        <v>-27.81354240000002</v>
       </c>
       <c r="O49">
-        <v>-7.986478080000001</v>
+        <v>-8.344062720000005</v>
       </c>
       <c r="P49">
-        <v>-18.63511552</v>
+        <v>-19.46947968000001</v>
       </c>
       <c r="Q49">
-        <v>3.864884479999997</v>
+        <v>3.030520319999987</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08862792649569282</v>
+        <v>0.08945154046676382</v>
       </c>
       <c r="T49">
-        <v>0.989097609600296</v>
+        <v>1.008118717477225</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1574392914092326</v>
+        <v>0.1541593061715402</v>
       </c>
       <c r="W49">
-        <v>0.1691861902850261</v>
+        <v>0.1698448113207547</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5247976380307753</v>
+        <v>0.513864353905134</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1280403104766795</v>
+        <v>0.1295903104766795</v>
       </c>
       <c r="C50">
-        <v>-73.24480886358435</v>
+        <v>-82.02372643849591</v>
       </c>
       <c r="D50">
-        <v>153.6831911364156</v>
+        <v>150.8402735615041</v>
       </c>
       <c r="E50">
-        <v>247.328</v>
+        <v>253.264</v>
       </c>
       <c r="F50">
-        <v>284.928</v>
+        <v>290.864</v>
       </c>
       <c r="G50">
         <v>58</v>
@@ -5375,37 +5375,37 @@
         <v>29.4</v>
       </c>
       <c r="M50">
-        <v>57.2135424</v>
+        <v>58.40549120000001</v>
       </c>
       <c r="N50">
-        <v>-27.8135424</v>
+        <v>-29.00549120000001</v>
       </c>
       <c r="O50">
-        <v>-8.34406272</v>
+        <v>-8.701647360000003</v>
       </c>
       <c r="P50">
-        <v>-19.46947968</v>
+        <v>-20.30384384000001</v>
       </c>
       <c r="Q50">
-        <v>3.030520319999997</v>
+        <v>2.196156159999994</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08945154046676382</v>
+        <v>0.09030745302493566</v>
       </c>
       <c r="T50">
-        <v>1.008118717477225</v>
+        <v>1.027885751153249</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1541593061715403</v>
+        <v>0.1510131978823251</v>
       </c>
       <c r="W50">
-        <v>0.1698448113207547</v>
+        <v>0.1704765498652291</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5138643539051342</v>
+        <v>0.503377326274417</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1295903104766795</v>
+        <v>0.1489095417483603</v>
       </c>
       <c r="C51">
-        <v>-82.02372643849591</v>
+        <v>-116.2220781142528</v>
       </c>
       <c r="D51">
-        <v>150.8402735615041</v>
+        <v>122.5779218857472</v>
       </c>
       <c r="E51">
-        <v>253.264</v>
+        <v>259.2</v>
       </c>
       <c r="F51">
-        <v>290.864</v>
+        <v>296.8</v>
       </c>
       <c r="G51">
         <v>58</v>
@@ -5457,45 +5457,45 @@
         <v>29.4</v>
       </c>
       <c r="M51">
-        <v>58.40549120000001</v>
+        <v>69.98544000000001</v>
       </c>
       <c r="N51">
-        <v>-29.00549120000001</v>
+        <v>-40.58544000000001</v>
       </c>
       <c r="O51">
-        <v>-8.701647360000003</v>
+        <v>-12.175632</v>
       </c>
       <c r="P51">
-        <v>-20.30384384000001</v>
+        <v>-28.40980800000001</v>
       </c>
       <c r="Q51">
-        <v>2.196156159999994</v>
+        <v>-5.909808000000009</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09030745302493566</v>
+        <v>0.09173606462879598</v>
       </c>
       <c r="T51">
-        <v>1.027885751153249</v>
+        <v>1.060879090734318</v>
       </c>
       <c r="U51">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1510131978823251</v>
+        <v>0.1260262134523981</v>
       </c>
       <c r="W51">
-        <v>0.1704765498652291</v>
+        <v>0.2060830188679245</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.503377326274417</v>
+        <v>0.4200873781746602</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1489095417483603</v>
+        <v>0.1508095417483603</v>
       </c>
       <c r="C52">
-        <v>-116.2220781142528</v>
+        <v>-124.3759532492669</v>
       </c>
       <c r="D52">
-        <v>122.5779218857472</v>
+        <v>120.3600467507331</v>
       </c>
       <c r="E52">
-        <v>259.2</v>
+        <v>265.136</v>
       </c>
       <c r="F52">
-        <v>296.8</v>
+        <v>302.736</v>
       </c>
       <c r="G52">
         <v>58</v>
@@ -5539,37 +5539,37 @@
         <v>29.4</v>
       </c>
       <c r="M52">
-        <v>69.98544000000001</v>
+        <v>71.3851488</v>
       </c>
       <c r="N52">
-        <v>-40.58544000000001</v>
+        <v>-41.9851488</v>
       </c>
       <c r="O52">
-        <v>-12.175632</v>
+        <v>-12.59554464</v>
       </c>
       <c r="P52">
-        <v>-28.40980800000001</v>
+        <v>-29.38960416</v>
       </c>
       <c r="Q52">
-        <v>-5.909808000000009</v>
+        <v>-6.889604159999998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09173606462879598</v>
+        <v>0.0926735353355061</v>
       </c>
       <c r="T52">
-        <v>1.060879090734318</v>
+        <v>1.082529684422774</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1260262134523981</v>
+        <v>0.1235551112278413</v>
       </c>
       <c r="W52">
-        <v>0.2060830188679245</v>
+        <v>0.206665704772475</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4200873781746602</v>
+        <v>0.411850370759471</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1508095417483603</v>
+        <v>0.1527095417483603</v>
       </c>
       <c r="C53">
-        <v>-124.3759532492669</v>
+        <v>-132.450996080118</v>
       </c>
       <c r="D53">
-        <v>120.3600467507331</v>
+        <v>118.2210039198821</v>
       </c>
       <c r="E53">
-        <v>265.136</v>
+        <v>271.072</v>
       </c>
       <c r="F53">
-        <v>302.736</v>
+        <v>308.672</v>
       </c>
       <c r="G53">
         <v>58</v>
@@ -5621,37 +5621,37 @@
         <v>29.4</v>
       </c>
       <c r="M53">
-        <v>71.3851488</v>
+        <v>72.78485760000001</v>
       </c>
       <c r="N53">
-        <v>-41.9851488</v>
+        <v>-43.38485760000001</v>
       </c>
       <c r="O53">
-        <v>-12.59554464</v>
+        <v>-13.01545728</v>
       </c>
       <c r="P53">
-        <v>-29.38960416</v>
+        <v>-30.36940032000001</v>
       </c>
       <c r="Q53">
-        <v>-6.889604159999998</v>
+        <v>-7.869400320000008</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0926735353355061</v>
+        <v>0.09365006732166248</v>
       </c>
       <c r="T53">
-        <v>1.082529684422774</v>
+        <v>1.105082386181581</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1235551112278413</v>
+        <v>0.1211790513965366</v>
       </c>
       <c r="W53">
-        <v>0.206665704772475</v>
+        <v>0.2072259796806967</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.411850370759471</v>
+        <v>0.4039301713217887</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1527095417483603</v>
+        <v>0.1546095417483603</v>
       </c>
       <c r="C54">
-        <v>-132.450996080118</v>
+        <v>-140.4513362458659</v>
       </c>
       <c r="D54">
-        <v>118.2210039198821</v>
+        <v>116.156663754134</v>
       </c>
       <c r="E54">
-        <v>271.072</v>
+        <v>277.008</v>
       </c>
       <c r="F54">
-        <v>308.672</v>
+        <v>314.608</v>
       </c>
       <c r="G54">
         <v>58</v>
@@ -5703,37 +5703,37 @@
         <v>29.4</v>
       </c>
       <c r="M54">
-        <v>72.78485760000001</v>
+        <v>74.18456640000001</v>
       </c>
       <c r="N54">
-        <v>-43.38485760000001</v>
+        <v>-44.78456640000001</v>
       </c>
       <c r="O54">
-        <v>-13.01545728</v>
+        <v>-13.43536992</v>
       </c>
       <c r="P54">
-        <v>-30.36940032000001</v>
+        <v>-31.34919648000001</v>
       </c>
       <c r="Q54">
-        <v>-7.869400320000008</v>
+        <v>-8.849196480000007</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09365006732166248</v>
+        <v>0.09466815386042124</v>
       </c>
       <c r="T54">
-        <v>1.105082386181581</v>
+        <v>1.128594777376934</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1211790513965366</v>
+        <v>0.1188926542003755</v>
       </c>
       <c r="W54">
-        <v>0.2072259796806967</v>
+        <v>0.2077651121395515</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4039301713217887</v>
+        <v>0.3963088473345852</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1546095417483603</v>
+        <v>0.1565095417483603</v>
       </c>
       <c r="C55">
-        <v>-140.4513362458659</v>
+        <v>-148.3808198936846</v>
       </c>
       <c r="D55">
-        <v>116.156663754134</v>
+        <v>114.1631801063154</v>
       </c>
       <c r="E55">
-        <v>277.008</v>
+        <v>282.9440000000001</v>
       </c>
       <c r="F55">
-        <v>314.608</v>
+        <v>320.544</v>
       </c>
       <c r="G55">
         <v>58</v>
@@ -5785,37 +5785,37 @@
         <v>29.4</v>
       </c>
       <c r="M55">
-        <v>74.18456640000001</v>
+        <v>75.58427520000001</v>
       </c>
       <c r="N55">
-        <v>-44.78456640000001</v>
+        <v>-46.18427520000001</v>
       </c>
       <c r="O55">
-        <v>-13.43536992</v>
+        <v>-13.85528256</v>
       </c>
       <c r="P55">
-        <v>-31.34919648000001</v>
+        <v>-32.32899264000001</v>
       </c>
       <c r="Q55">
-        <v>-8.849196480000007</v>
+        <v>-9.82899264000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09466815386042124</v>
+        <v>0.09573050503129997</v>
       </c>
       <c r="T55">
-        <v>1.128594777376934</v>
+        <v>1.153129446450346</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1188926542003755</v>
+        <v>0.1166909383818501</v>
       </c>
       <c r="W55">
-        <v>0.2077651121395515</v>
+        <v>0.2082842767295598</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3963088473345852</v>
+        <v>0.3889697946061669</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1565095417483603</v>
+        <v>0.1584095417483603</v>
       </c>
       <c r="C56">
-        <v>-148.3808198936846</v>
+        <v>-156.2430335948887</v>
       </c>
       <c r="D56">
-        <v>114.1631801063154</v>
+        <v>112.2369664051114</v>
       </c>
       <c r="E56">
-        <v>282.9440000000001</v>
+        <v>288.88</v>
       </c>
       <c r="F56">
-        <v>320.544</v>
+        <v>326.48</v>
       </c>
       <c r="G56">
         <v>58</v>
@@ -5867,37 +5867,37 @@
         <v>29.4</v>
       </c>
       <c r="M56">
-        <v>75.58427520000001</v>
+        <v>76.98398400000001</v>
       </c>
       <c r="N56">
-        <v>-46.18427520000001</v>
+        <v>-47.58398400000001</v>
       </c>
       <c r="O56">
-        <v>-13.85528256</v>
+        <v>-14.2751952</v>
       </c>
       <c r="P56">
-        <v>-32.32899264000001</v>
+        <v>-33.3087888</v>
       </c>
       <c r="Q56">
-        <v>-9.82899264000001</v>
+        <v>-10.8087888</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09573050503129997</v>
+        <v>0.0968400718097733</v>
       </c>
       <c r="T56">
-        <v>1.153129446450346</v>
+        <v>1.178754545260354</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1166909383818501</v>
+        <v>0.1145692849567255</v>
       </c>
       <c r="W56">
-        <v>0.2082842767295598</v>
+        <v>0.2087845626072042</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3889697946061669</v>
+        <v>0.3818976165224184</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1584095417483603</v>
+        <v>0.1603095417483603</v>
       </c>
       <c r="C57">
-        <v>-156.2430335948887</v>
+        <v>-164.041325880001</v>
       </c>
       <c r="D57">
-        <v>112.2369664051114</v>
+        <v>110.3746741199991</v>
       </c>
       <c r="E57">
-        <v>288.88</v>
+        <v>294.816</v>
       </c>
       <c r="F57">
-        <v>326.48</v>
+        <v>332.4160000000001</v>
       </c>
       <c r="G57">
         <v>58</v>
@@ -5949,37 +5949,37 @@
         <v>29.4</v>
       </c>
       <c r="M57">
-        <v>76.98398400000001</v>
+        <v>78.38369280000002</v>
       </c>
       <c r="N57">
-        <v>-47.58398400000001</v>
+        <v>-48.98369280000002</v>
       </c>
       <c r="O57">
-        <v>-14.2751952</v>
+        <v>-14.69510784000001</v>
       </c>
       <c r="P57">
-        <v>-33.3087888</v>
+        <v>-34.28858496000002</v>
       </c>
       <c r="Q57">
-        <v>-10.8087888</v>
+        <v>-11.78858496000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.0968400718097733</v>
+        <v>0.09800007344181361</v>
       </c>
       <c r="T57">
-        <v>1.178754545260354</v>
+        <v>1.205544421288998</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1145692849567255</v>
+        <v>0.1125234048682126</v>
       </c>
       <c r="W57">
-        <v>0.2087845626072042</v>
+        <v>0.2092669811320755</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3818976165224184</v>
+        <v>0.3750780162273751</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1603095417483603</v>
+        <v>0.1622095417483603</v>
       </c>
       <c r="C58">
-        <v>-164.041325880001</v>
+        <v>-171.7788266648879</v>
       </c>
       <c r="D58">
-        <v>110.3746741199991</v>
+        <v>108.5731733351121</v>
       </c>
       <c r="E58">
-        <v>294.816</v>
+        <v>300.7520000000001</v>
       </c>
       <c r="F58">
-        <v>332.4160000000001</v>
+        <v>338.352</v>
       </c>
       <c r="G58">
         <v>58</v>
@@ -6031,37 +6031,37 @@
         <v>29.4</v>
       </c>
       <c r="M58">
-        <v>78.38369280000002</v>
+        <v>79.7834016</v>
       </c>
       <c r="N58">
-        <v>-48.98369280000002</v>
+        <v>-50.38340160000001</v>
       </c>
       <c r="O58">
-        <v>-14.69510784000001</v>
+        <v>-15.11502048</v>
       </c>
       <c r="P58">
-        <v>-34.28858496000002</v>
+        <v>-35.26838112</v>
       </c>
       <c r="Q58">
-        <v>-11.78858496000002</v>
+        <v>-12.76838112</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09800007344181361</v>
+        <v>0.09921402863813486</v>
       </c>
       <c r="T58">
-        <v>1.205544421288998</v>
+        <v>1.233580338063161</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1125234048682126</v>
+        <v>0.1105493100459632</v>
       </c>
       <c r="W58">
-        <v>0.2092669811320755</v>
+        <v>0.2097324726911619</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3750780162273751</v>
+        <v>0.3684977001532108</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1622095417483603</v>
+        <v>0.1641095417483603</v>
       </c>
       <c r="C59">
-        <v>-171.7788266648879</v>
+        <v>-179.458464805043</v>
       </c>
       <c r="D59">
-        <v>108.5731733351121</v>
+        <v>106.8295351949571</v>
       </c>
       <c r="E59">
-        <v>300.7520000000001</v>
+        <v>306.6880000000001</v>
       </c>
       <c r="F59">
-        <v>338.352</v>
+        <v>344.2880000000001</v>
       </c>
       <c r="G59">
         <v>58</v>
@@ -6113,37 +6113,37 @@
         <v>29.4</v>
       </c>
       <c r="M59">
-        <v>79.7834016</v>
+        <v>81.18311040000002</v>
       </c>
       <c r="N59">
-        <v>-50.38340160000001</v>
+        <v>-51.78311040000002</v>
       </c>
       <c r="O59">
-        <v>-15.11502048</v>
+        <v>-15.53493312000001</v>
       </c>
       <c r="P59">
-        <v>-35.26838112</v>
+        <v>-36.24817728000001</v>
       </c>
       <c r="Q59">
-        <v>-12.76838112</v>
+        <v>-13.74817728000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09921402863813486</v>
+        <v>0.1004857912247571</v>
       </c>
       <c r="T59">
-        <v>1.233580338063161</v>
+        <v>1.262951298493236</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1105493100459632</v>
+        <v>0.1086432874589638</v>
       </c>
       <c r="W59">
-        <v>0.2097324726911619</v>
+        <v>0.2101819128171764</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3684977001532108</v>
+        <v>0.3621442915298795</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1641095417483602</v>
+        <v>0.1660095417483603</v>
       </c>
       <c r="C60">
-        <v>-179.458464805043</v>
+        <v>-187.0829839851203</v>
       </c>
       <c r="D60">
-        <v>106.8295351949571</v>
+        <v>105.1410160148797</v>
       </c>
       <c r="E60">
-        <v>306.688</v>
+        <v>312.624</v>
       </c>
       <c r="F60">
-        <v>344.288</v>
+        <v>350.224</v>
       </c>
       <c r="G60">
         <v>58</v>
@@ -6195,37 +6195,37 @@
         <v>29.4</v>
       </c>
       <c r="M60">
-        <v>81.1831104</v>
+        <v>82.5828192</v>
       </c>
       <c r="N60">
-        <v>-51.78311040000001</v>
+        <v>-53.1828192</v>
       </c>
       <c r="O60">
-        <v>-15.53493312</v>
+        <v>-15.95484576</v>
       </c>
       <c r="P60">
-        <v>-36.24817728000001</v>
+        <v>-37.22797344</v>
       </c>
       <c r="Q60">
-        <v>-13.74817728000001</v>
+        <v>-14.72797344</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1004857912247571</v>
+        <v>0.1018195910107268</v>
       </c>
       <c r="T60">
-        <v>1.262951298493236</v>
+        <v>1.293754988700388</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1086432874589639</v>
+        <v>0.106801875807117</v>
       </c>
       <c r="W60">
-        <v>0.2101819128171763</v>
+        <v>0.2106161176846818</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3621442915298796</v>
+        <v>0.3560062526903901</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1660095417483603</v>
+        <v>0.1679095417483603</v>
       </c>
       <c r="C61">
-        <v>-187.0829839851203</v>
+        <v>-194.6549571250405</v>
       </c>
       <c r="D61">
-        <v>105.1410160148797</v>
+        <v>103.5050428749596</v>
       </c>
       <c r="E61">
-        <v>312.624</v>
+        <v>318.5600000000001</v>
       </c>
       <c r="F61">
-        <v>350.224</v>
+        <v>356.16</v>
       </c>
       <c r="G61">
         <v>58</v>
@@ -6277,37 +6277,37 @@
         <v>29.4</v>
       </c>
       <c r="M61">
-        <v>82.5828192</v>
+        <v>83.98252800000002</v>
       </c>
       <c r="N61">
-        <v>-53.1828192</v>
+        <v>-54.58252800000002</v>
       </c>
       <c r="O61">
-        <v>-15.95484576</v>
+        <v>-16.3747584</v>
       </c>
       <c r="P61">
-        <v>-37.22797344</v>
+        <v>-38.20776960000001</v>
       </c>
       <c r="Q61">
-        <v>-14.72797344</v>
+        <v>-15.70776960000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1018195910107268</v>
+        <v>0.103220080785995</v>
       </c>
       <c r="T61">
-        <v>1.293754988700388</v>
+        <v>1.326098863417898</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.106801875807117</v>
+        <v>0.105021844543665</v>
       </c>
       <c r="W61">
-        <v>0.2106161176846818</v>
+        <v>0.2110358490566038</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3560062526903901</v>
+        <v>0.3500728151455502</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1679095417483603</v>
+        <v>0.1698095417483602</v>
       </c>
       <c r="C62">
-        <v>-194.6549571250405</v>
+        <v>-202.1767994617655</v>
       </c>
       <c r="D62">
-        <v>103.5050428749596</v>
+        <v>101.9192005382345</v>
       </c>
       <c r="E62">
-        <v>318.5600000000001</v>
+        <v>324.496</v>
       </c>
       <c r="F62">
-        <v>356.16</v>
+        <v>362.096</v>
       </c>
       <c r="G62">
         <v>58</v>
@@ -6359,37 +6359,37 @@
         <v>29.4</v>
       </c>
       <c r="M62">
-        <v>83.98252800000002</v>
+        <v>85.3822368</v>
       </c>
       <c r="N62">
-        <v>-54.58252800000002</v>
+        <v>-55.9822368</v>
       </c>
       <c r="O62">
-        <v>-16.3747584</v>
+        <v>-16.79467104</v>
       </c>
       <c r="P62">
-        <v>-38.20776960000001</v>
+        <v>-39.18756576</v>
       </c>
       <c r="Q62">
-        <v>-15.70776960000001</v>
+        <v>-16.68756576</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.103220080785995</v>
+        <v>0.1046923905497384</v>
       </c>
       <c r="T62">
-        <v>1.326098863417898</v>
+        <v>1.360101398377331</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.105021844543665</v>
+        <v>0.1033001749609821</v>
       </c>
       <c r="W62">
-        <v>0.2110358490566038</v>
+        <v>0.2114418187442004</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3500728151455502</v>
+        <v>0.3443339165366068</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1698095417483602</v>
+        <v>0.1717095417483603</v>
       </c>
       <c r="C63">
-        <v>-202.1767994617655</v>
+        <v>-209.6507804466353</v>
       </c>
       <c r="D63">
-        <v>101.9192005382345</v>
+        <v>100.3812195533647</v>
       </c>
       <c r="E63">
-        <v>324.496</v>
+        <v>330.432</v>
       </c>
       <c r="F63">
-        <v>362.096</v>
+        <v>368.032</v>
       </c>
       <c r="G63">
         <v>58</v>
@@ -6441,37 +6441,37 @@
         <v>29.4</v>
       </c>
       <c r="M63">
-        <v>85.3822368</v>
+        <v>86.78194560000001</v>
       </c>
       <c r="N63">
-        <v>-55.9822368</v>
+        <v>-57.38194560000002</v>
       </c>
       <c r="O63">
-        <v>-16.79467104</v>
+        <v>-17.21458368</v>
       </c>
       <c r="P63">
-        <v>-39.18756576</v>
+        <v>-40.16736192000001</v>
       </c>
       <c r="Q63">
-        <v>-16.68756576</v>
+        <v>-17.66736192000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1046923905497384</v>
+        <v>0.1062421903010473</v>
       </c>
       <c r="T63">
-        <v>1.360101398377331</v>
+        <v>1.395893540439892</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1033001749609821</v>
+        <v>0.1016340431067726</v>
       </c>
       <c r="W63">
-        <v>0.2114418187442004</v>
+        <v>0.211834692635423</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3443339165366068</v>
+        <v>0.3387801436892421</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1717095417483603</v>
+        <v>0.1736095417483602</v>
       </c>
       <c r="C64">
-        <v>-209.6507804466353</v>
+        <v>-217.0790345815175</v>
       </c>
       <c r="D64">
-        <v>100.3812195533647</v>
+        <v>98.88896541848253</v>
       </c>
       <c r="E64">
-        <v>330.432</v>
+        <v>336.3680000000001</v>
       </c>
       <c r="F64">
-        <v>368.032</v>
+        <v>373.968</v>
       </c>
       <c r="G64">
         <v>58</v>
@@ -6523,37 +6523,37 @@
         <v>29.4</v>
       </c>
       <c r="M64">
-        <v>86.78194560000001</v>
+        <v>88.18165440000001</v>
       </c>
       <c r="N64">
-        <v>-57.38194560000002</v>
+        <v>-58.78165440000001</v>
       </c>
       <c r="O64">
-        <v>-17.21458368</v>
+        <v>-17.63449632</v>
       </c>
       <c r="P64">
-        <v>-40.16736192000001</v>
+        <v>-41.14715808000001</v>
       </c>
       <c r="Q64">
-        <v>-17.66736192000001</v>
+        <v>-18.64715808000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1062421903010473</v>
+        <v>0.1078757630118864</v>
       </c>
       <c r="T64">
-        <v>1.395893540439892</v>
+        <v>1.433620392884214</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1016340431067726</v>
+        <v>0.1000208043273001</v>
       </c>
       <c r="W64">
-        <v>0.211834692635423</v>
+        <v>0.2122150943396227</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3387801436892421</v>
+        <v>0.3334026810910002</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1736095417483602</v>
+        <v>0.1755095417483603</v>
       </c>
       <c r="C65">
-        <v>-217.0790345815175</v>
+        <v>-224.4635713025833</v>
       </c>
       <c r="D65">
-        <v>98.88896541848253</v>
+        <v>97.44042869741671</v>
       </c>
       <c r="E65">
-        <v>336.3680000000001</v>
+        <v>342.304</v>
       </c>
       <c r="F65">
-        <v>373.968</v>
+        <v>379.904</v>
       </c>
       <c r="G65">
         <v>58</v>
@@ -6605,37 +6605,37 @@
         <v>29.4</v>
       </c>
       <c r="M65">
-        <v>88.18165440000001</v>
+        <v>89.5813632</v>
       </c>
       <c r="N65">
-        <v>-58.78165440000001</v>
+        <v>-60.1813632</v>
       </c>
       <c r="O65">
-        <v>-17.63449632</v>
+        <v>-18.05440896</v>
       </c>
       <c r="P65">
-        <v>-41.14715808000001</v>
+        <v>-42.12695424</v>
       </c>
       <c r="Q65">
-        <v>-18.64715808000001</v>
+        <v>-19.62695424</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1078757630118864</v>
+        <v>0.1096000897622166</v>
       </c>
       <c r="T65">
-        <v>1.433620392884214</v>
+        <v>1.473443181575442</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1000208043273001</v>
+        <v>0.09845797925968601</v>
       </c>
       <c r="W65">
-        <v>0.2122150943396227</v>
+        <v>0.212583608490566</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3334026810910002</v>
+        <v>0.3281932641989533</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1755095417483603</v>
+        <v>0.1774095417483602</v>
       </c>
       <c r="C66">
-        <v>-224.4635713025833</v>
+        <v>-231.8062840079514</v>
       </c>
       <c r="D66">
-        <v>97.44042869741671</v>
+        <v>96.03371599204864</v>
       </c>
       <c r="E66">
-        <v>342.304</v>
+        <v>348.24</v>
       </c>
       <c r="F66">
-        <v>379.904</v>
+        <v>385.84</v>
       </c>
       <c r="G66">
         <v>58</v>
@@ -6687,37 +6687,37 @@
         <v>29.4</v>
       </c>
       <c r="M66">
-        <v>89.5813632</v>
+        <v>90.98107200000001</v>
       </c>
       <c r="N66">
-        <v>-60.1813632</v>
+        <v>-61.58107200000001</v>
       </c>
       <c r="O66">
-        <v>-18.05440896</v>
+        <v>-18.4743216</v>
       </c>
       <c r="P66">
-        <v>-42.12695424</v>
+        <v>-43.10675040000001</v>
       </c>
       <c r="Q66">
-        <v>-19.62695424</v>
+        <v>-20.60675040000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1096000897622166</v>
+        <v>0.1114229494697085</v>
       </c>
       <c r="T66">
-        <v>1.473443181575442</v>
+        <v>1.515541558191883</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09845797925968601</v>
+        <v>0.09694324111722928</v>
       </c>
       <c r="W66">
-        <v>0.212583608490566</v>
+        <v>0.2129407837445573</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3281932641989533</v>
+        <v>0.3231441370574309</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1774095417483602</v>
+        <v>0.1793095417483603</v>
       </c>
       <c r="C67">
-        <v>-231.8062840079514</v>
+        <v>-239.1089583144875</v>
       </c>
       <c r="D67">
-        <v>96.03371599204864</v>
+        <v>94.66704168551253</v>
       </c>
       <c r="E67">
-        <v>348.24</v>
+        <v>354.176</v>
       </c>
       <c r="F67">
-        <v>385.84</v>
+        <v>391.776</v>
       </c>
       <c r="G67">
         <v>58</v>
@@ -6769,37 +6769,37 @@
         <v>29.4</v>
       </c>
       <c r="M67">
-        <v>90.98107200000001</v>
+        <v>92.38078080000001</v>
       </c>
       <c r="N67">
-        <v>-61.58107200000001</v>
+        <v>-62.98078080000001</v>
       </c>
       <c r="O67">
-        <v>-18.4743216</v>
+        <v>-18.89423424</v>
       </c>
       <c r="P67">
-        <v>-43.10675040000001</v>
+        <v>-44.08654656000001</v>
       </c>
       <c r="Q67">
-        <v>-20.60675040000001</v>
+        <v>-21.58654656000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1114229494697085</v>
+        <v>0.1133530362188176</v>
       </c>
       <c r="T67">
-        <v>1.515541558191883</v>
+        <v>1.560116309903409</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09694324111722928</v>
+        <v>0.0954744041306046</v>
       </c>
       <c r="W67">
-        <v>0.2129407837445573</v>
+        <v>0.2132871355060035</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3231441370574309</v>
+        <v>0.3182480137686821</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1793095417483603</v>
+        <v>0.1812095417483602</v>
       </c>
       <c r="C68">
-        <v>-239.1089583144875</v>
+        <v>-246.3732796194715</v>
       </c>
       <c r="D68">
-        <v>94.66704168551253</v>
+        <v>93.3387203805285</v>
       </c>
       <c r="E68">
-        <v>354.176</v>
+        <v>360.1120000000001</v>
       </c>
       <c r="F68">
-        <v>391.776</v>
+        <v>397.712</v>
       </c>
       <c r="G68">
         <v>58</v>
@@ -6851,37 +6851,37 @@
         <v>29.4</v>
       </c>
       <c r="M68">
-        <v>92.38078080000001</v>
+        <v>93.78048960000001</v>
       </c>
       <c r="N68">
-        <v>-62.98078080000001</v>
+        <v>-64.3804896</v>
       </c>
       <c r="O68">
-        <v>-18.89423424</v>
+        <v>-19.31414688</v>
       </c>
       <c r="P68">
-        <v>-44.08654656000001</v>
+        <v>-45.06634272000001</v>
       </c>
       <c r="Q68">
-        <v>-21.58654656000001</v>
+        <v>-22.56634272000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1133530362188176</v>
+        <v>0.1154000979224181</v>
       </c>
       <c r="T68">
-        <v>1.560116309903409</v>
+        <v>1.607392561718664</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0954744041306046</v>
+        <v>0.09404941302417767</v>
       </c>
       <c r="W68">
-        <v>0.2132871355060035</v>
+        <v>0.2136231484088989</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3182480137686821</v>
+        <v>0.3134980434139256</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1812095417483602</v>
+        <v>0.1831095417483602</v>
       </c>
       <c r="C69">
-        <v>-246.3732796194715</v>
+        <v>-253.6008400344645</v>
       </c>
       <c r="D69">
-        <v>93.3387203805285</v>
+        <v>92.04715996553551</v>
       </c>
       <c r="E69">
-        <v>360.1120000000001</v>
+        <v>366.048</v>
       </c>
       <c r="F69">
-        <v>397.712</v>
+        <v>403.648</v>
       </c>
       <c r="G69">
         <v>58</v>
@@ -6933,37 +6933,37 @@
         <v>29.4</v>
       </c>
       <c r="M69">
-        <v>93.78048960000001</v>
+        <v>95.18019840000001</v>
       </c>
       <c r="N69">
-        <v>-64.3804896</v>
+        <v>-65.78019840000002</v>
       </c>
       <c r="O69">
-        <v>-19.31414688</v>
+        <v>-19.73405952000001</v>
       </c>
       <c r="P69">
-        <v>-45.06634272000001</v>
+        <v>-46.04613888000002</v>
       </c>
       <c r="Q69">
-        <v>-22.56634272000001</v>
+        <v>-23.54613888000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1154000979224181</v>
+        <v>0.1175751009824937</v>
       </c>
       <c r="T69">
-        <v>1.607392561718664</v>
+        <v>1.657623579272372</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09404941302417767</v>
+        <v>0.09266633342088094</v>
       </c>
       <c r="W69">
-        <v>0.2136231484088989</v>
+        <v>0.2139492785793563</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3134980434139256</v>
+        <v>0.3088877780696031</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1831095417483602</v>
+        <v>0.1850095417483603</v>
       </c>
       <c r="C70">
-        <v>-253.6008400344645</v>
+        <v>-260.7931447513542</v>
       </c>
       <c r="D70">
-        <v>92.04715996553551</v>
+        <v>90.79085524864583</v>
       </c>
       <c r="E70">
-        <v>366.048</v>
+        <v>371.984</v>
       </c>
       <c r="F70">
-        <v>403.648</v>
+        <v>409.5840000000001</v>
       </c>
       <c r="G70">
         <v>58</v>
@@ -7015,37 +7015,37 @@
         <v>29.4</v>
       </c>
       <c r="M70">
-        <v>95.18019840000001</v>
+        <v>96.57990720000002</v>
       </c>
       <c r="N70">
-        <v>-65.78019840000002</v>
+        <v>-67.17990720000003</v>
       </c>
       <c r="O70">
-        <v>-19.73405952000001</v>
+        <v>-20.15397216000001</v>
       </c>
       <c r="P70">
-        <v>-46.04613888000002</v>
+        <v>-47.02593504000002</v>
       </c>
       <c r="Q70">
-        <v>-23.54613888000002</v>
+        <v>-24.52593504000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1175751009824937</v>
+        <v>0.1198904268206387</v>
       </c>
       <c r="T70">
-        <v>1.657623579272372</v>
+        <v>1.711095307635998</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09266633342088094</v>
+        <v>0.09132334308144786</v>
       </c>
       <c r="W70">
-        <v>0.2139492785793563</v>
+        <v>0.2142659557013946</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3088877780696031</v>
+        <v>0.3044111436048261</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1850095417483603</v>
+        <v>0.1869095417483603</v>
       </c>
       <c r="C71">
-        <v>-260.7931447513542</v>
+        <v>-267.9516178940992</v>
       </c>
       <c r="D71">
-        <v>90.79085524864583</v>
+        <v>89.5683821059008</v>
       </c>
       <c r="E71">
-        <v>371.984</v>
+        <v>377.9200000000001</v>
       </c>
       <c r="F71">
-        <v>409.5840000000001</v>
+        <v>415.52</v>
       </c>
       <c r="G71">
         <v>58</v>
@@ -7097,37 +7097,37 @@
         <v>29.4</v>
       </c>
       <c r="M71">
-        <v>96.57990720000002</v>
+        <v>97.97961600000001</v>
       </c>
       <c r="N71">
-        <v>-67.17990720000003</v>
+        <v>-68.57961600000002</v>
       </c>
       <c r="O71">
-        <v>-20.15397216000001</v>
+        <v>-20.57388480000001</v>
       </c>
       <c r="P71">
-        <v>-47.02593504000002</v>
+        <v>-48.00573120000001</v>
       </c>
       <c r="Q71">
-        <v>-24.52593504000002</v>
+        <v>-25.50573120000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1198904268206387</v>
+        <v>0.12236010771466</v>
       </c>
       <c r="T71">
-        <v>1.711095307635998</v>
+        <v>1.768131817890531</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09132334308144786</v>
+        <v>0.09001872389457005</v>
       </c>
       <c r="W71">
-        <v>0.2142659557013946</v>
+        <v>0.2145735849056604</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3044111436048261</v>
+        <v>0.3000624129819002</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1869095417483603</v>
+        <v>0.1888095417483603</v>
       </c>
       <c r="C72">
-        <v>-267.9516178940992</v>
+        <v>-275.0776079040013</v>
       </c>
       <c r="D72">
-        <v>89.5683821059008</v>
+        <v>88.37839209599881</v>
       </c>
       <c r="E72">
-        <v>377.9200000000001</v>
+        <v>383.8560000000001</v>
       </c>
       <c r="F72">
-        <v>415.52</v>
+        <v>421.4560000000001</v>
       </c>
       <c r="G72">
         <v>58</v>
@@ -7179,37 +7179,37 @@
         <v>29.4</v>
       </c>
       <c r="M72">
-        <v>97.97961600000001</v>
+        <v>99.37932480000002</v>
       </c>
       <c r="N72">
-        <v>-68.57961600000002</v>
+        <v>-69.97932480000003</v>
       </c>
       <c r="O72">
-        <v>-20.57388480000001</v>
+        <v>-20.99379744000001</v>
       </c>
       <c r="P72">
-        <v>-48.00573120000001</v>
+        <v>-48.98552736000002</v>
       </c>
       <c r="Q72">
-        <v>-25.50573120000001</v>
+        <v>-26.48552736000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.12236010771466</v>
+        <v>0.1250001114289586</v>
       </c>
       <c r="T72">
-        <v>1.768131817890531</v>
+        <v>1.829101880576411</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09001872389457005</v>
+        <v>0.08875085454394228</v>
       </c>
       <c r="W72">
-        <v>0.2145735849056604</v>
+        <v>0.2148725484985384</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3000624129819002</v>
+        <v>0.295836181813141</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1888095417483603</v>
+        <v>0.1907095417483602</v>
       </c>
       <c r="C73">
-        <v>-275.0776079040012</v>
+        <v>-282.1723925013191</v>
       </c>
       <c r="D73">
-        <v>88.37839209599881</v>
+        <v>87.21960749868087</v>
       </c>
       <c r="E73">
-        <v>383.856</v>
+        <v>389.792</v>
       </c>
       <c r="F73">
-        <v>421.456</v>
+        <v>427.392</v>
       </c>
       <c r="G73">
         <v>58</v>
@@ -7261,37 +7261,37 @@
         <v>29.4</v>
       </c>
       <c r="M73">
-        <v>99.37932480000001</v>
+        <v>100.7790336</v>
       </c>
       <c r="N73">
-        <v>-69.9793248</v>
+        <v>-71.37903360000001</v>
       </c>
       <c r="O73">
-        <v>-20.99379744</v>
+        <v>-21.41371008</v>
       </c>
       <c r="P73">
-        <v>-48.98552736000001</v>
+        <v>-49.96532352000001</v>
       </c>
       <c r="Q73">
-        <v>-26.48552736000001</v>
+        <v>-27.46532352000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1250001114289586</v>
+        <v>0.1278286868371357</v>
       </c>
       <c r="T73">
-        <v>1.829101880576411</v>
+        <v>1.894426947739854</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08875085454394231</v>
+        <v>0.08751820378638756</v>
       </c>
       <c r="W73">
-        <v>0.2148725484985384</v>
+        <v>0.2151632075471698</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2958361818131411</v>
+        <v>0.2917273459546251</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1907095417483602</v>
+        <v>0.1926095417483603</v>
       </c>
       <c r="C74">
-        <v>-282.1723925013191</v>
+        <v>-289.237183261606</v>
       </c>
       <c r="D74">
-        <v>87.21960749868087</v>
+        <v>86.09081673839407</v>
       </c>
       <c r="E74">
-        <v>389.792</v>
+        <v>395.7280000000001</v>
       </c>
       <c r="F74">
-        <v>427.392</v>
+        <v>433.328</v>
       </c>
       <c r="G74">
         <v>58</v>
@@ -7343,37 +7343,37 @@
         <v>29.4</v>
       </c>
       <c r="M74">
-        <v>100.7790336</v>
+        <v>102.1787424</v>
       </c>
       <c r="N74">
-        <v>-71.37903360000001</v>
+        <v>-72.77874240000003</v>
       </c>
       <c r="O74">
-        <v>-21.41371008</v>
+        <v>-21.83362272000001</v>
       </c>
       <c r="P74">
-        <v>-49.96532352000001</v>
+        <v>-50.94511968000002</v>
       </c>
       <c r="Q74">
-        <v>-27.46532352000001</v>
+        <v>-28.44511968000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1278286868371357</v>
+        <v>0.1308667863496221</v>
       </c>
       <c r="T74">
-        <v>1.894426947739854</v>
+        <v>1.964590908767256</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08751820378638756</v>
+        <v>0.08631932428246443</v>
       </c>
       <c r="W74">
-        <v>0.2151632075471698</v>
+        <v>0.2154459033341949</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2917273459546251</v>
+        <v>0.2877310809415481</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1926095417483603</v>
+        <v>0.1945095417483602</v>
       </c>
       <c r="C75">
-        <v>-289.237183261606</v>
+        <v>-296.2731298412258</v>
       </c>
       <c r="D75">
-        <v>86.09081673839407</v>
+        <v>84.99087015877424</v>
       </c>
       <c r="E75">
-        <v>395.7280000000001</v>
+        <v>401.664</v>
       </c>
       <c r="F75">
-        <v>433.328</v>
+        <v>439.264</v>
       </c>
       <c r="G75">
         <v>58</v>
@@ -7425,37 +7425,37 @@
         <v>29.4</v>
       </c>
       <c r="M75">
-        <v>102.1787424</v>
+        <v>103.5784512</v>
       </c>
       <c r="N75">
-        <v>-72.77874240000003</v>
+        <v>-74.17845120000001</v>
       </c>
       <c r="O75">
-        <v>-21.83362272000001</v>
+        <v>-22.25353536</v>
       </c>
       <c r="P75">
-        <v>-50.94511968000002</v>
+        <v>-51.92491584000001</v>
       </c>
       <c r="Q75">
-        <v>-28.44511968000002</v>
+        <v>-29.42491584000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1308667863496221</v>
+        <v>0.1341385858246076</v>
       </c>
       <c r="T75">
-        <v>1.964590908767256</v>
+        <v>2.040152097565997</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08631932428246443</v>
+        <v>0.08515284692729601</v>
       </c>
       <c r="W75">
-        <v>0.2154459033341949</v>
+        <v>0.2157209586945436</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2877310809415481</v>
+        <v>0.2838428230909866</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1945095417483602</v>
+        <v>0.1964095417483603</v>
       </c>
       <c r="C76">
-        <v>-296.2731298412258</v>
+        <v>-303.2813238830316</v>
       </c>
       <c r="D76">
-        <v>84.99087015877424</v>
+        <v>83.91867611696848</v>
       </c>
       <c r="E76">
-        <v>401.664</v>
+        <v>407.6</v>
       </c>
       <c r="F76">
-        <v>439.264</v>
+        <v>445.2</v>
       </c>
       <c r="G76">
         <v>58</v>
@@ -7507,37 +7507,37 @@
         <v>29.4</v>
       </c>
       <c r="M76">
-        <v>103.5784512</v>
+        <v>104.97816</v>
       </c>
       <c r="N76">
-        <v>-74.17845120000001</v>
+        <v>-75.57816000000003</v>
       </c>
       <c r="O76">
-        <v>-22.25353536</v>
+        <v>-22.67344800000001</v>
       </c>
       <c r="P76">
-        <v>-51.92491584000001</v>
+        <v>-52.90471200000002</v>
       </c>
       <c r="Q76">
-        <v>-29.42491584000001</v>
+        <v>-30.40471200000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1341385858246076</v>
+        <v>0.137672129257592</v>
       </c>
       <c r="T76">
-        <v>2.040152097565997</v>
+        <v>2.121758181468637</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08515284692729601</v>
+        <v>0.08401747563493205</v>
       </c>
       <c r="W76">
-        <v>0.2157209586945436</v>
+        <v>0.215988679245283</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2838428230909866</v>
+        <v>0.2800582521164401</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1964095417483603</v>
+        <v>0.1983095417483602</v>
       </c>
       <c r="C77">
-        <v>-303.2813238830316</v>
+        <v>-310.2628026300946</v>
       </c>
       <c r="D77">
-        <v>83.91867611696848</v>
+        <v>82.87319736990544</v>
       </c>
       <c r="E77">
-        <v>407.6</v>
+        <v>413.5360000000001</v>
       </c>
       <c r="F77">
-        <v>445.2</v>
+        <v>451.136</v>
       </c>
       <c r="G77">
         <v>58</v>
@@ -7589,37 +7589,37 @@
         <v>29.4</v>
       </c>
       <c r="M77">
-        <v>104.97816</v>
+        <v>106.3778688</v>
       </c>
       <c r="N77">
-        <v>-75.57816000000003</v>
+        <v>-76.97786880000001</v>
       </c>
       <c r="O77">
-        <v>-22.67344800000001</v>
+        <v>-23.09336064</v>
       </c>
       <c r="P77">
-        <v>-52.90471200000002</v>
+        <v>-53.88450816000001</v>
       </c>
       <c r="Q77">
-        <v>-30.40471200000002</v>
+        <v>-31.38450816000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.137672129257592</v>
+        <v>0.1415001346433249</v>
       </c>
       <c r="T77">
-        <v>2.121758181468637</v>
+        <v>2.210164772363163</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08401747563493205</v>
+        <v>0.08291198253447242</v>
       </c>
       <c r="W77">
-        <v>0.215988679245283</v>
+        <v>0.2162493545183714</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2800582521164401</v>
+        <v>0.2763732751149082</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1983095417483602</v>
+        <v>0.2002095417483603</v>
       </c>
       <c r="C78">
-        <v>-310.2628026300946</v>
+        <v>-317.2185522726357</v>
       </c>
       <c r="D78">
-        <v>82.87319736990544</v>
+        <v>81.85344772736433</v>
       </c>
       <c r="E78">
-        <v>413.5360000000001</v>
+        <v>419.472</v>
       </c>
       <c r="F78">
-        <v>451.136</v>
+        <v>457.072</v>
       </c>
       <c r="G78">
         <v>58</v>
@@ -7671,37 +7671,37 @@
         <v>29.4</v>
       </c>
       <c r="M78">
-        <v>106.3778688</v>
+        <v>107.7775776</v>
       </c>
       <c r="N78">
-        <v>-76.97786880000001</v>
+        <v>-78.3775776</v>
       </c>
       <c r="O78">
-        <v>-23.09336064</v>
+        <v>-23.51327328</v>
       </c>
       <c r="P78">
-        <v>-53.88450816000001</v>
+        <v>-54.86430432</v>
       </c>
       <c r="Q78">
-        <v>-31.38450816000001</v>
+        <v>-32.36430432</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1415001346433249</v>
+        <v>0.1456610100625999</v>
       </c>
       <c r="T78">
-        <v>2.210164772363163</v>
+        <v>2.306258892900692</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08291198253447242</v>
+        <v>0.08183520354051824</v>
       </c>
       <c r="W78">
-        <v>0.2162493545183714</v>
+        <v>0.2165032590051458</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2763732751149082</v>
+        <v>0.2727840118017275</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2002095417483603</v>
+        <v>0.2021095417483603</v>
       </c>
       <c r="C79">
-        <v>-317.2185522726357</v>
+        <v>-324.1495110508552</v>
       </c>
       <c r="D79">
-        <v>81.85344772736433</v>
+        <v>80.85848894914487</v>
       </c>
       <c r="E79">
-        <v>419.472</v>
+        <v>425.408</v>
       </c>
       <c r="F79">
-        <v>457.072</v>
+        <v>463.008</v>
       </c>
       <c r="G79">
         <v>58</v>
@@ -7753,37 +7753,37 @@
         <v>29.4</v>
       </c>
       <c r="M79">
-        <v>107.7775776</v>
+        <v>109.1772864</v>
       </c>
       <c r="N79">
-        <v>-78.3775776</v>
+        <v>-79.77728640000001</v>
       </c>
       <c r="O79">
-        <v>-23.51327328</v>
+        <v>-23.93318592</v>
       </c>
       <c r="P79">
-        <v>-54.86430432</v>
+        <v>-55.84410048000001</v>
       </c>
       <c r="Q79">
-        <v>-32.36430432</v>
+        <v>-33.34410048000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1456610100625999</v>
+        <v>0.1502001468836272</v>
       </c>
       <c r="T79">
-        <v>2.306258892900692</v>
+        <v>2.411088842577996</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08183520354051824</v>
+        <v>0.08078603426435774</v>
       </c>
       <c r="W79">
-        <v>0.2165032590051458</v>
+        <v>0.2167506531204645</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2727840118017275</v>
+        <v>0.2692867808811925</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2021095417483603</v>
+        <v>0.2040095417483603</v>
       </c>
       <c r="C80">
-        <v>-324.1495110508552</v>
+        <v>-331.0565721341856</v>
       </c>
       <c r="D80">
-        <v>80.85848894914487</v>
+        <v>79.88742786581444</v>
       </c>
       <c r="E80">
-        <v>425.408</v>
+        <v>431.3440000000001</v>
       </c>
       <c r="F80">
-        <v>463.008</v>
+        <v>468.944</v>
       </c>
       <c r="G80">
         <v>58</v>
@@ -7835,37 +7835,37 @@
         <v>29.4</v>
       </c>
       <c r="M80">
-        <v>109.1772864</v>
+        <v>110.5769952</v>
       </c>
       <c r="N80">
-        <v>-79.77728640000001</v>
+        <v>-81.17699520000002</v>
       </c>
       <c r="O80">
-        <v>-23.93318592</v>
+        <v>-24.35309856000001</v>
       </c>
       <c r="P80">
-        <v>-55.84410048000001</v>
+        <v>-56.82389664000002</v>
       </c>
       <c r="Q80">
-        <v>-33.34410048000001</v>
+        <v>-34.32389664000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1502001468836272</v>
+        <v>0.1551715824495142</v>
       </c>
       <c r="T80">
-        <v>2.411088842577996</v>
+        <v>2.525902596986473</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08078603426435774</v>
+        <v>0.07976342623569498</v>
       </c>
       <c r="W80">
-        <v>0.2167506531204645</v>
+        <v>0.2169917840936231</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2692867808811925</v>
+        <v>0.2658780874523166</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2040095417483603</v>
+        <v>0.2059095417483603</v>
       </c>
       <c r="C81">
-        <v>-331.0565721341856</v>
+        <v>-337.9405862955378</v>
       </c>
       <c r="D81">
-        <v>79.88742786581444</v>
+        <v>78.93941370446225</v>
       </c>
       <c r="E81">
-        <v>431.3440000000001</v>
+        <v>437.2800000000001</v>
       </c>
       <c r="F81">
-        <v>468.944</v>
+        <v>474.8800000000001</v>
       </c>
       <c r="G81">
         <v>58</v>
@@ -7917,37 +7917,37 @@
         <v>29.4</v>
       </c>
       <c r="M81">
-        <v>110.5769952</v>
+        <v>111.976704</v>
       </c>
       <c r="N81">
-        <v>-81.17699520000002</v>
+        <v>-82.57670400000001</v>
       </c>
       <c r="O81">
-        <v>-24.35309856000001</v>
+        <v>-24.7730112</v>
       </c>
       <c r="P81">
-        <v>-56.82389664000002</v>
+        <v>-57.80369280000001</v>
       </c>
       <c r="Q81">
-        <v>-34.32389664000002</v>
+        <v>-35.30369280000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1551715824495142</v>
+        <v>0.16064016157199</v>
       </c>
       <c r="T81">
-        <v>2.525902596986473</v>
+        <v>2.652197726835796</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07976342623569498</v>
+        <v>0.07876638340774879</v>
       </c>
       <c r="W81">
-        <v>0.2169917840936231</v>
+        <v>0.2172268867924529</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2658780874523166</v>
+        <v>0.2625546113591627</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2059095417483603</v>
+        <v>0.2078095417483603</v>
       </c>
       <c r="C82">
-        <v>-337.9405862955378</v>
+        <v>-344.8023643973697</v>
       </c>
       <c r="D82">
-        <v>78.93941370446225</v>
+        <v>78.01363560263032</v>
       </c>
       <c r="E82">
-        <v>437.2800000000001</v>
+        <v>443.216</v>
       </c>
       <c r="F82">
-        <v>474.8800000000001</v>
+        <v>480.816</v>
       </c>
       <c r="G82">
         <v>58</v>
@@ -7999,37 +7999,37 @@
         <v>29.4</v>
       </c>
       <c r="M82">
-        <v>111.976704</v>
+        <v>113.3764128</v>
       </c>
       <c r="N82">
-        <v>-82.57670400000001</v>
+        <v>-83.97641280000002</v>
       </c>
       <c r="O82">
-        <v>-24.7730112</v>
+        <v>-25.19292384000001</v>
       </c>
       <c r="P82">
-        <v>-57.80369280000001</v>
+        <v>-58.78348896000001</v>
       </c>
       <c r="Q82">
-        <v>-35.30369280000001</v>
+        <v>-36.28348896000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.16064016157199</v>
+        <v>0.1666843806020947</v>
       </c>
       <c r="T82">
-        <v>2.652197726835796</v>
+        <v>2.791787080879786</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07876638340774879</v>
+        <v>0.07779395892123338</v>
       </c>
       <c r="W82">
-        <v>0.2172268867924529</v>
+        <v>0.2174561844863732</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2625546113591627</v>
+        <v>0.2593131964041112</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2078095417483603</v>
+        <v>0.2097095417483602</v>
       </c>
       <c r="C83">
-        <v>-344.8023643973697</v>
+        <v>-351.6426797048493</v>
       </c>
       <c r="D83">
-        <v>78.01363560263032</v>
+        <v>77.10932029515078</v>
       </c>
       <c r="E83">
-        <v>443.216</v>
+        <v>449.152</v>
       </c>
       <c r="F83">
-        <v>480.816</v>
+        <v>486.7520000000001</v>
       </c>
       <c r="G83">
         <v>58</v>
@@ -8081,37 +8081,37 @@
         <v>29.4</v>
       </c>
       <c r="M83">
-        <v>113.3764128</v>
+        <v>114.7761216</v>
       </c>
       <c r="N83">
-        <v>-83.97641280000002</v>
+        <v>-85.37612160000003</v>
       </c>
       <c r="O83">
-        <v>-25.19292384000001</v>
+        <v>-25.61283648000001</v>
       </c>
       <c r="P83">
-        <v>-58.78348896000001</v>
+        <v>-59.76328512000002</v>
       </c>
       <c r="Q83">
-        <v>-36.28348896000001</v>
+        <v>-37.26328512000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1666843806020947</v>
+        <v>0.1734001795244333</v>
       </c>
       <c r="T83">
-        <v>2.791787080879786</v>
+        <v>2.946886363150885</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07779395892123338</v>
+        <v>0.07684525210512078</v>
       </c>
       <c r="W83">
-        <v>0.2174561844863732</v>
+        <v>0.2176798895536125</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2593131964041112</v>
+        <v>0.2561508403504025</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2097095417483602</v>
+        <v>0.2116095417483603</v>
       </c>
       <c r="C84">
-        <v>-351.6426797048493</v>
+        <v>-358.4622700399769</v>
       </c>
       <c r="D84">
-        <v>77.10932029515078</v>
+        <v>76.22572996002313</v>
       </c>
       <c r="E84">
-        <v>449.152</v>
+        <v>455.0880000000001</v>
       </c>
       <c r="F84">
-        <v>486.7520000000001</v>
+        <v>492.688</v>
       </c>
       <c r="G84">
         <v>58</v>
@@ -8163,37 +8163,37 @@
         <v>29.4</v>
       </c>
       <c r="M84">
-        <v>114.7761216</v>
+        <v>116.1758304</v>
       </c>
       <c r="N84">
-        <v>-85.37612160000003</v>
+        <v>-86.77583040000002</v>
       </c>
       <c r="O84">
-        <v>-25.61283648000001</v>
+        <v>-26.03274912000001</v>
       </c>
       <c r="P84">
-        <v>-59.76328512000002</v>
+        <v>-60.74308128000001</v>
       </c>
       <c r="Q84">
-        <v>-37.26328512000002</v>
+        <v>-38.24308128000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1734001795244333</v>
+        <v>0.1809060724376353</v>
       </c>
       <c r="T84">
-        <v>2.946886363150885</v>
+        <v>3.120232619806819</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07684525210512078</v>
+        <v>0.07591940569421571</v>
       </c>
       <c r="W84">
-        <v>0.2176798895536125</v>
+        <v>0.2178982041373039</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2561508403504025</v>
+        <v>0.2530646856473856</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2116095417483603</v>
+        <v>0.2135095417483603</v>
       </c>
       <c r="C85">
-        <v>-358.4622700399769</v>
+        <v>-365.2618397892841</v>
       </c>
       <c r="D85">
-        <v>76.22572996002313</v>
+        <v>75.36216021071604</v>
       </c>
       <c r="E85">
-        <v>455.0880000000001</v>
+        <v>461.0240000000001</v>
       </c>
       <c r="F85">
-        <v>492.688</v>
+        <v>498.6240000000001</v>
       </c>
       <c r="G85">
         <v>58</v>
@@ -8245,37 +8245,37 @@
         <v>29.4</v>
       </c>
       <c r="M85">
-        <v>116.1758304</v>
+        <v>117.5755392</v>
       </c>
       <c r="N85">
-        <v>-86.77583040000002</v>
+        <v>-88.17553920000003</v>
       </c>
       <c r="O85">
-        <v>-26.03274912000001</v>
+        <v>-26.45266176000001</v>
       </c>
       <c r="P85">
-        <v>-60.74308128000001</v>
+        <v>-61.72287744000002</v>
       </c>
       <c r="Q85">
-        <v>-38.24308128000001</v>
+        <v>-39.22287744000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1809060724376353</v>
+        <v>0.1893502019649875</v>
       </c>
       <c r="T85">
-        <v>3.120232619806819</v>
+        <v>3.315247158544746</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07591940569421571</v>
+        <v>0.07501560324547503</v>
       </c>
       <c r="W85">
-        <v>0.2178982041373039</v>
+        <v>0.218111320754717</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2530646856473856</v>
+        <v>0.2500520108182501</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2135095417483602</v>
+        <v>0.2154095417483603</v>
       </c>
       <c r="C86">
-        <v>-365.2618397892841</v>
+        <v>-372.042061776587</v>
       </c>
       <c r="D86">
-        <v>75.36216021071598</v>
+        <v>74.51793822341301</v>
       </c>
       <c r="E86">
-        <v>461.024</v>
+        <v>466.96</v>
       </c>
       <c r="F86">
-        <v>498.624</v>
+        <v>504.56</v>
       </c>
       <c r="G86">
         <v>58</v>
@@ -8327,37 +8327,37 @@
         <v>29.4</v>
       </c>
       <c r="M86">
-        <v>117.5755392</v>
+        <v>118.975248</v>
       </c>
       <c r="N86">
-        <v>-88.1755392</v>
+        <v>-89.57524800000002</v>
       </c>
       <c r="O86">
-        <v>-26.45266176</v>
+        <v>-26.8725744</v>
       </c>
       <c r="P86">
-        <v>-61.72287744</v>
+        <v>-62.70267360000001</v>
       </c>
       <c r="Q86">
-        <v>-39.22287744</v>
+        <v>-40.20267360000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1893502019649874</v>
+        <v>0.1989202154293199</v>
       </c>
       <c r="T86">
-        <v>3.315247158544744</v>
+        <v>3.536263635781061</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07501560324547506</v>
+        <v>0.07413306673670475</v>
       </c>
       <c r="W86">
-        <v>0.218111320754717</v>
+        <v>0.218319422863485</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2500520108182502</v>
+        <v>0.2471102224556825</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2154095417483603</v>
+        <v>0.2173095417483603</v>
       </c>
       <c r="C87">
-        <v>-372.042061776587</v>
+        <v>-378.8035790112621</v>
       </c>
       <c r="D87">
-        <v>74.51793822341301</v>
+        <v>73.69242098873795</v>
       </c>
       <c r="E87">
-        <v>466.96</v>
+        <v>472.8960000000001</v>
       </c>
       <c r="F87">
-        <v>504.56</v>
+        <v>510.496</v>
       </c>
       <c r="G87">
         <v>58</v>
@@ -8409,37 +8409,37 @@
         <v>29.4</v>
       </c>
       <c r="M87">
-        <v>118.975248</v>
+        <v>120.3749568</v>
       </c>
       <c r="N87">
-        <v>-89.57524800000002</v>
+        <v>-90.9749568</v>
       </c>
       <c r="O87">
-        <v>-26.8725744</v>
+        <v>-27.29248704</v>
       </c>
       <c r="P87">
-        <v>-62.70267360000001</v>
+        <v>-63.68246976</v>
       </c>
       <c r="Q87">
-        <v>-40.20267360000001</v>
+        <v>-41.18246976</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1989202154293199</v>
+        <v>0.2098573736742713</v>
       </c>
       <c r="T87">
-        <v>3.536263635781061</v>
+        <v>3.788853895479707</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07413306673670475</v>
+        <v>0.07327105433278958</v>
       </c>
       <c r="W87">
-        <v>0.218319422863485</v>
+        <v>0.2185226853883282</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2471102224556825</v>
+        <v>0.2442368477759653</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2173095417483603</v>
+        <v>0.2192095417483603</v>
       </c>
       <c r="C88">
-        <v>-378.8035790112621</v>
+        <v>-385.5470063215873</v>
       </c>
       <c r="D88">
-        <v>73.69242098873795</v>
+        <v>72.88499367841271</v>
       </c>
       <c r="E88">
-        <v>472.8960000000001</v>
+        <v>478.832</v>
       </c>
       <c r="F88">
-        <v>510.496</v>
+        <v>516.432</v>
       </c>
       <c r="G88">
         <v>58</v>
@@ -8491,37 +8491,37 @@
         <v>29.4</v>
       </c>
       <c r="M88">
-        <v>120.3749568</v>
+        <v>121.7746656</v>
       </c>
       <c r="N88">
-        <v>-90.9749568</v>
+        <v>-92.37466560000001</v>
       </c>
       <c r="O88">
-        <v>-27.29248704</v>
+        <v>-27.71239968</v>
       </c>
       <c r="P88">
-        <v>-63.68246976</v>
+        <v>-64.66226592000001</v>
       </c>
       <c r="Q88">
-        <v>-41.18246976</v>
+        <v>-42.16226592000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2098573736742713</v>
+        <v>0.2224771716492153</v>
       </c>
       <c r="T88">
-        <v>3.788853895479707</v>
+        <v>4.080304195131993</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07327105433278958</v>
+        <v>0.07242885830597591</v>
       </c>
       <c r="W88">
-        <v>0.2185226853883282</v>
+        <v>0.2187212752114509</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2442368477759653</v>
+        <v>0.2414295276865863</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2192095417483603</v>
+        <v>0.2211095417483603</v>
       </c>
       <c r="C89">
-        <v>-385.5470063215873</v>
+        <v>-392.2729318818728</v>
       </c>
       <c r="D89">
-        <v>72.88499367841271</v>
+        <v>72.09506811812724</v>
       </c>
       <c r="E89">
-        <v>478.832</v>
+        <v>484.768</v>
       </c>
       <c r="F89">
-        <v>516.432</v>
+        <v>522.3680000000001</v>
       </c>
       <c r="G89">
         <v>58</v>
@@ -8573,37 +8573,37 @@
         <v>29.4</v>
       </c>
       <c r="M89">
-        <v>121.7746656</v>
+        <v>123.1743744</v>
       </c>
       <c r="N89">
-        <v>-92.37466560000001</v>
+        <v>-93.77437440000003</v>
       </c>
       <c r="O89">
-        <v>-27.71239968</v>
+        <v>-28.13231232000001</v>
       </c>
       <c r="P89">
-        <v>-64.66226592000001</v>
+        <v>-65.64206208000002</v>
       </c>
       <c r="Q89">
-        <v>-42.16226592000001</v>
+        <v>-43.14206208000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2224771716492153</v>
+        <v>0.2372002692866499</v>
       </c>
       <c r="T89">
-        <v>4.080304195131993</v>
+        <v>4.420329544726326</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07242885830597591</v>
+        <v>0.07160580309795345</v>
       </c>
       <c r="W89">
-        <v>0.2187212752114509</v>
+        <v>0.2189153516295026</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2414295276865863</v>
+        <v>0.2386860103265115</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2211095417483603</v>
+        <v>0.2230095417483602</v>
       </c>
       <c r="C90">
-        <v>-392.2729318818728</v>
+        <v>-398.9819186413497</v>
       </c>
       <c r="D90">
-        <v>72.09506811812724</v>
+        <v>71.32208135865029</v>
       </c>
       <c r="E90">
-        <v>484.768</v>
+        <v>490.704</v>
       </c>
       <c r="F90">
-        <v>522.3680000000001</v>
+        <v>528.304</v>
       </c>
       <c r="G90">
         <v>58</v>
@@ -8655,37 +8655,37 @@
         <v>29.4</v>
       </c>
       <c r="M90">
-        <v>123.1743744</v>
+        <v>124.5740832</v>
       </c>
       <c r="N90">
-        <v>-93.77437440000003</v>
+        <v>-95.17408320000001</v>
       </c>
       <c r="O90">
-        <v>-28.13231232000001</v>
+        <v>-28.55222496</v>
       </c>
       <c r="P90">
-        <v>-65.64206208000002</v>
+        <v>-66.62185824000001</v>
       </c>
       <c r="Q90">
-        <v>-43.14206208000002</v>
+        <v>-44.12185824000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2372002692866499</v>
+        <v>0.2546002937672544</v>
       </c>
       <c r="T90">
-        <v>4.420329544726326</v>
+        <v>4.822177685155991</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07160580309795345</v>
+        <v>0.07080124351258318</v>
       </c>
       <c r="W90">
-        <v>0.2189153516295026</v>
+        <v>0.2191050667797329</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2386860103265115</v>
+        <v>0.2360041450419439</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2230095417483602</v>
+        <v>0.2249095417483603</v>
       </c>
       <c r="C91">
-        <v>-398.9819186413497</v>
+        <v>-405.6745056621117</v>
       </c>
       <c r="D91">
-        <v>71.32208135865029</v>
+        <v>70.56549433788831</v>
       </c>
       <c r="E91">
-        <v>490.704</v>
+        <v>496.64</v>
       </c>
       <c r="F91">
-        <v>528.304</v>
+        <v>534.24</v>
       </c>
       <c r="G91">
         <v>58</v>
@@ -8737,37 +8737,37 @@
         <v>29.4</v>
       </c>
       <c r="M91">
-        <v>124.5740832</v>
+        <v>125.973792</v>
       </c>
       <c r="N91">
-        <v>-95.17408320000001</v>
+        <v>-96.573792</v>
       </c>
       <c r="O91">
-        <v>-28.55222496</v>
+        <v>-28.9721376</v>
       </c>
       <c r="P91">
-        <v>-66.62185824000001</v>
+        <v>-67.6016544</v>
       </c>
       <c r="Q91">
-        <v>-44.12185824000001</v>
+        <v>-45.1016544</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2546002937672544</v>
+        <v>0.2754803231439799</v>
       </c>
       <c r="T91">
-        <v>4.822177685155991</v>
+        <v>5.304395453671592</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07080124351258318</v>
+        <v>0.07001456302911005</v>
       </c>
       <c r="W91">
-        <v>0.2191050667797329</v>
+        <v>0.2192905660377359</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2360041450419439</v>
+        <v>0.2333818767637003</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2249095417483603</v>
+        <v>0.2268095417483603</v>
       </c>
       <c r="C92">
-        <v>-405.6745056621117</v>
+        <v>-412.3512093727944</v>
       </c>
       <c r="D92">
-        <v>70.56549433788831</v>
+        <v>69.8247906272056</v>
       </c>
       <c r="E92">
-        <v>496.64</v>
+        <v>502.576</v>
       </c>
       <c r="F92">
-        <v>534.24</v>
+        <v>540.176</v>
       </c>
       <c r="G92">
         <v>58</v>
@@ -8819,37 +8819,37 @@
         <v>29.4</v>
       </c>
       <c r="M92">
-        <v>125.973792</v>
+        <v>127.3735008</v>
       </c>
       <c r="N92">
-        <v>-96.573792</v>
+        <v>-97.97350080000001</v>
       </c>
       <c r="O92">
-        <v>-28.9721376</v>
+        <v>-29.39205024</v>
       </c>
       <c r="P92">
-        <v>-67.6016544</v>
+        <v>-68.58145056000001</v>
       </c>
       <c r="Q92">
-        <v>-45.1016544</v>
+        <v>-46.08145056000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2754803231439799</v>
+        <v>0.3010003590488666</v>
       </c>
       <c r="T92">
-        <v>5.304395453671592</v>
+        <v>5.89377272630177</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07001456302911005</v>
+        <v>0.06924517222659235</v>
       </c>
       <c r="W92">
-        <v>0.2192905660377359</v>
+        <v>0.2194719883889695</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2333818767637003</v>
+        <v>0.2308172407553079</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2268095417483603</v>
+        <v>0.2287095417483603</v>
       </c>
       <c r="C93">
-        <v>-412.3512093727944</v>
+        <v>-419.0125247441172</v>
       </c>
       <c r="D93">
-        <v>69.8247906272056</v>
+        <v>69.09947525588288</v>
       </c>
       <c r="E93">
-        <v>502.576</v>
+        <v>508.5120000000001</v>
       </c>
       <c r="F93">
-        <v>540.176</v>
+        <v>546.1120000000001</v>
       </c>
       <c r="G93">
         <v>58</v>
@@ -8901,37 +8901,37 @@
         <v>29.4</v>
       </c>
       <c r="M93">
-        <v>127.3735008</v>
+        <v>128.7732096</v>
       </c>
       <c r="N93">
-        <v>-97.97350080000001</v>
+        <v>-99.37320960000002</v>
       </c>
       <c r="O93">
-        <v>-29.39205024</v>
+        <v>-29.81196288000001</v>
       </c>
       <c r="P93">
-        <v>-68.58145056000001</v>
+        <v>-69.56124672000001</v>
       </c>
       <c r="Q93">
-        <v>-46.08145056000001</v>
+        <v>-47.06124672000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3010003590488666</v>
+        <v>0.332900403929975</v>
       </c>
       <c r="T93">
-        <v>5.89377272630177</v>
+        <v>6.630494317089493</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06924517222659235</v>
+        <v>0.0684925073110859</v>
       </c>
       <c r="W93">
-        <v>0.2194719883889695</v>
+        <v>0.2196494667760459</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2308172407553079</v>
+        <v>0.2283083577036198</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2287095417483603</v>
+        <v>0.2306095417483602</v>
       </c>
       <c r="C94">
-        <v>-419.0125247441172</v>
+        <v>-425.6589263919117</v>
       </c>
       <c r="D94">
-        <v>69.09947525588288</v>
+        <v>68.38907360808834</v>
       </c>
       <c r="E94">
-        <v>508.5120000000001</v>
+        <v>514.448</v>
       </c>
       <c r="F94">
-        <v>546.1120000000001</v>
+        <v>552.048</v>
       </c>
       <c r="G94">
         <v>58</v>
@@ -8983,37 +8983,37 @@
         <v>29.4</v>
       </c>
       <c r="M94">
-        <v>128.7732096</v>
+        <v>130.1729184</v>
       </c>
       <c r="N94">
-        <v>-99.37320960000002</v>
+        <v>-100.7729184</v>
       </c>
       <c r="O94">
-        <v>-29.81196288000001</v>
+        <v>-30.23187552</v>
       </c>
       <c r="P94">
-        <v>-69.56124672000001</v>
+        <v>-70.54104288000001</v>
       </c>
       <c r="Q94">
-        <v>-47.06124672000001</v>
+        <v>-48.04104288000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.332900403929975</v>
+        <v>0.3739147473485429</v>
       </c>
       <c r="T94">
-        <v>6.630494317089493</v>
+        <v>7.577707790959421</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0684925073110859</v>
+        <v>0.06775602873784843</v>
       </c>
       <c r="W94">
-        <v>0.2196494667760459</v>
+        <v>0.2198231284236153</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2283083577036198</v>
+        <v>0.2258534291261615</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2306095417483602</v>
+        <v>0.2325095417483603</v>
       </c>
       <c r="C95">
-        <v>-425.6589263919117</v>
+        <v>-432.2908696128022</v>
       </c>
       <c r="D95">
-        <v>68.38907360808834</v>
+        <v>67.6931303871978</v>
       </c>
       <c r="E95">
-        <v>514.448</v>
+        <v>520.384</v>
       </c>
       <c r="F95">
-        <v>552.048</v>
+        <v>557.984</v>
       </c>
       <c r="G95">
         <v>58</v>
@@ -9065,37 +9065,37 @@
         <v>29.4</v>
       </c>
       <c r="M95">
-        <v>130.1729184</v>
+        <v>131.5726272</v>
       </c>
       <c r="N95">
-        <v>-100.7729184</v>
+        <v>-102.1726272</v>
       </c>
       <c r="O95">
-        <v>-30.23187552</v>
+        <v>-30.65178816000001</v>
       </c>
       <c r="P95">
-        <v>-70.54104288000001</v>
+        <v>-71.52083904000001</v>
       </c>
       <c r="Q95">
-        <v>-48.04104288000001</v>
+        <v>-49.02083904000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3739147473485429</v>
+        <v>0.4286005385733002</v>
       </c>
       <c r="T95">
-        <v>7.577707790959421</v>
+        <v>8.840659089452661</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06775602873784843</v>
+        <v>0.06703521992148832</v>
       </c>
       <c r="W95">
-        <v>0.2198231284236153</v>
+        <v>0.2199930951425131</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2258534291261615</v>
+        <v>0.2234507330716279</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2325095417483603</v>
+        <v>0.2344095417483603</v>
       </c>
       <c r="C96">
-        <v>-432.2908696128022</v>
+        <v>-438.908791357288</v>
       </c>
       <c r="D96">
-        <v>67.6931303871978</v>
+        <v>67.01120864271213</v>
       </c>
       <c r="E96">
-        <v>520.384</v>
+        <v>526.3200000000001</v>
       </c>
       <c r="F96">
-        <v>557.984</v>
+        <v>563.9200000000001</v>
       </c>
       <c r="G96">
         <v>58</v>
@@ -9147,37 +9147,37 @@
         <v>29.4</v>
       </c>
       <c r="M96">
-        <v>131.5726272</v>
+        <v>132.972336</v>
       </c>
       <c r="N96">
-        <v>-102.1726272</v>
+        <v>-103.572336</v>
       </c>
       <c r="O96">
-        <v>-30.65178816000001</v>
+        <v>-31.0717008</v>
       </c>
       <c r="P96">
-        <v>-71.52083904000001</v>
+        <v>-72.5006352</v>
       </c>
       <c r="Q96">
-        <v>-49.02083904000001</v>
+        <v>-50.0006352</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4286005385733002</v>
+        <v>0.5051606462879604</v>
       </c>
       <c r="T96">
-        <v>8.840659089452661</v>
+        <v>10.6087909073432</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06703521992148832</v>
+        <v>0.06632958602757794</v>
       </c>
       <c r="W96">
-        <v>0.2199930951425131</v>
+        <v>0.2201594836146971</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2234507330716279</v>
+        <v>0.2210986200919265</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2344095417483603</v>
+        <v>0.2363095417483603</v>
       </c>
       <c r="C97">
-        <v>-438.908791357288</v>
+        <v>-445.5131111445947</v>
       </c>
       <c r="D97">
-        <v>67.01120864271213</v>
+        <v>66.34288885540543</v>
       </c>
       <c r="E97">
-        <v>526.3200000000001</v>
+        <v>532.2560000000001</v>
       </c>
       <c r="F97">
-        <v>563.9200000000001</v>
+        <v>569.8560000000001</v>
       </c>
       <c r="G97">
         <v>58</v>
@@ -9229,37 +9229,37 @@
         <v>29.4</v>
       </c>
       <c r="M97">
-        <v>132.972336</v>
+        <v>134.3720448</v>
       </c>
       <c r="N97">
-        <v>-103.572336</v>
+        <v>-104.9720448</v>
       </c>
       <c r="O97">
-        <v>-31.0717008</v>
+        <v>-31.49161344000001</v>
       </c>
       <c r="P97">
-        <v>-72.5006352</v>
+        <v>-73.48043136000001</v>
       </c>
       <c r="Q97">
-        <v>-50.0006352</v>
+        <v>-50.98043136000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5051606462879604</v>
+        <v>0.6200008078599506</v>
       </c>
       <c r="T97">
-        <v>10.6087909073432</v>
+        <v>13.260988634179</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06632958602757794</v>
+        <v>0.06563865283979066</v>
       </c>
       <c r="W97">
-        <v>0.2201594836146971</v>
+        <v>0.2203224056603774</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2210986200919265</v>
+        <v>0.2187955094659689</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2363095417483602</v>
+        <v>0.2382095417483603</v>
       </c>
       <c r="C98">
-        <v>-445.5131111445945</v>
+        <v>-452.1042319233246</v>
       </c>
       <c r="D98">
-        <v>66.34288885540549</v>
+        <v>65.68776807667548</v>
       </c>
       <c r="E98">
-        <v>532.256</v>
+        <v>538.192</v>
       </c>
       <c r="F98">
-        <v>569.856</v>
+        <v>575.792</v>
       </c>
       <c r="G98">
         <v>58</v>
@@ -9311,37 +9311,37 @@
         <v>29.4</v>
       </c>
       <c r="M98">
-        <v>134.3720448</v>
+        <v>135.7717536</v>
       </c>
       <c r="N98">
-        <v>-104.9720448</v>
+        <v>-106.3717536</v>
       </c>
       <c r="O98">
-        <v>-31.49161343999999</v>
+        <v>-31.91152608</v>
       </c>
       <c r="P98">
-        <v>-73.48043136</v>
+        <v>-74.46022752</v>
       </c>
       <c r="Q98">
-        <v>-50.98043136</v>
+        <v>-51.96022752</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6200008078599492</v>
+        <v>0.8114010771465988</v>
       </c>
       <c r="T98">
-        <v>13.26098863417897</v>
+        <v>17.68131817890529</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06563865283979067</v>
+        <v>0.06496196569711241</v>
       </c>
       <c r="W98">
-        <v>0.2203224056603774</v>
+        <v>0.2204819684886209</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2187955094659689</v>
+        <v>0.2165398856570414</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2382095417483603</v>
+        <v>0.2401095417483602</v>
       </c>
       <c r="C99">
-        <v>-452.1042319233246</v>
+        <v>-458.682540881612</v>
       </c>
       <c r="D99">
-        <v>65.68776807667548</v>
+        <v>65.0454591183881</v>
       </c>
       <c r="E99">
-        <v>538.192</v>
+        <v>544.128</v>
       </c>
       <c r="F99">
-        <v>575.792</v>
+        <v>581.7280000000001</v>
       </c>
       <c r="G99">
         <v>58</v>
@@ -9393,37 +9393,37 @@
         <v>29.4</v>
       </c>
       <c r="M99">
-        <v>135.7717536</v>
+        <v>137.1714624</v>
       </c>
       <c r="N99">
-        <v>-106.3717536</v>
+        <v>-107.7714624</v>
       </c>
       <c r="O99">
-        <v>-31.91152608</v>
+        <v>-32.33143872</v>
       </c>
       <c r="P99">
-        <v>-74.46022752</v>
+        <v>-75.44002368000002</v>
       </c>
       <c r="Q99">
-        <v>-51.96022752</v>
+        <v>-52.94002368000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8114010771465988</v>
+        <v>1.194201615719898</v>
       </c>
       <c r="T99">
-        <v>17.68131817890529</v>
+        <v>26.52197726835794</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06496196569711241</v>
+        <v>0.06429908849612145</v>
       </c>
       <c r="W99">
-        <v>0.2204819684886209</v>
+        <v>0.2206382749326146</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2165398856570414</v>
+        <v>0.2143302949870716</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2401095417483602</v>
+        <v>0.2420095417483603</v>
       </c>
       <c r="C100">
-        <v>-458.682540881612</v>
+        <v>-465.2484102102068</v>
       </c>
       <c r="D100">
-        <v>65.0454591183881</v>
+        <v>64.41558978979323</v>
       </c>
       <c r="E100">
-        <v>544.128</v>
+        <v>550.064</v>
       </c>
       <c r="F100">
-        <v>581.7280000000001</v>
+        <v>587.664</v>
       </c>
       <c r="G100">
         <v>58</v>
@@ -9475,37 +9475,37 @@
         <v>29.4</v>
       </c>
       <c r="M100">
-        <v>137.1714624</v>
+        <v>138.5711712</v>
       </c>
       <c r="N100">
-        <v>-107.7714624</v>
+        <v>-109.1711712</v>
       </c>
       <c r="O100">
-        <v>-32.33143872</v>
+        <v>-32.75135136</v>
       </c>
       <c r="P100">
-        <v>-75.44002368000002</v>
+        <v>-76.41981984</v>
       </c>
       <c r="Q100">
-        <v>-52.94002368000002</v>
+        <v>-53.91981984</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.194201615719898</v>
+        <v>2.342603231439796</v>
       </c>
       <c r="T100">
-        <v>26.52197726835794</v>
+        <v>53.04395453671586</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06429908849612145</v>
+        <v>0.06364960275373641</v>
       </c>
       <c r="W100">
-        <v>0.2206382749326146</v>
+        <v>0.220791423670669</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2143302949870716</v>
+        <v>0.2121653425124548</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2420095417483603</v>
-      </c>
-      <c r="C101">
-        <v>-465.2484102102068</v>
-      </c>
-      <c r="D101">
-        <v>64.41558978979323</v>
-      </c>
-      <c r="E101">
-        <v>550.064</v>
-      </c>
-      <c r="F101">
-        <v>587.664</v>
-      </c>
-      <c r="G101">
-        <v>58</v>
-      </c>
-      <c r="H101">
-        <v>556</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>51.9</v>
-      </c>
-      <c r="K101">
-        <v>22.5</v>
-      </c>
-      <c r="L101">
-        <v>29.4</v>
-      </c>
-      <c r="M101">
-        <v>138.5711712</v>
-      </c>
-      <c r="N101">
-        <v>-109.1711712</v>
-      </c>
-      <c r="O101">
-        <v>-32.75135136</v>
-      </c>
-      <c r="P101">
-        <v>-76.41981984</v>
-      </c>
-      <c r="Q101">
-        <v>-53.91981984</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.342603231439796</v>
-      </c>
-      <c r="T101">
-        <v>53.04395453671586</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06364960275373641</v>
-      </c>
-      <c r="W101">
-        <v>0.220791423670669</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2121653425124548</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
